--- a/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
+++ b/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THANH_TOAN_KY_PHU_LUC_03A" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIEN_DO_THI_CONG_WBS" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOSO_KCS_NGHIEM_THU" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHAN_TICH_VAT_TU_WBS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TONG_HOP_VAT_TU_TOAN_BO" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,9 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -288,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -394,15 +398,38 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6036,7 +6063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6053,6 +6080,7 @@
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -6074,6 +6102,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -6194,7 +6223,7 @@
         <f>I8*E8</f>
         <v/>
       </c>
-      <c r="K8" s="49">
+      <c r="K8" s="61">
         <f>H8*E8</f>
         <v/>
       </c>
@@ -6247,7 +6276,7 @@
         <f>I9*E9</f>
         <v/>
       </c>
-      <c r="K9" s="49">
+      <c r="K9" s="61">
         <f>H9*E9</f>
         <v/>
       </c>
@@ -6300,7 +6329,7 @@
         <f>I10*E10</f>
         <v/>
       </c>
-      <c r="K10" s="49">
+      <c r="K10" s="61">
         <f>H10*E10</f>
         <v/>
       </c>
@@ -6353,7 +6382,7 @@
         <f>I11*E11</f>
         <v/>
       </c>
-      <c r="K11" s="49">
+      <c r="K11" s="61">
         <f>H11*E11</f>
         <v/>
       </c>
@@ -6406,7 +6435,7 @@
         <f>I12*E12</f>
         <v/>
       </c>
-      <c r="K12" s="49">
+      <c r="K12" s="61">
         <f>H12*E12</f>
         <v/>
       </c>
@@ -6459,7 +6488,7 @@
         <f>I13*E13</f>
         <v/>
       </c>
-      <c r="K13" s="49">
+      <c r="K13" s="61">
         <f>H13*E13</f>
         <v/>
       </c>
@@ -6519,7 +6548,7 @@
         <f>I15*E15</f>
         <v/>
       </c>
-      <c r="K15" s="49">
+      <c r="K15" s="61">
         <f>H15*E15</f>
         <v/>
       </c>
@@ -6572,7 +6601,7 @@
         <f>I16*E16</f>
         <v/>
       </c>
-      <c r="K16" s="49">
+      <c r="K16" s="61">
         <f>H16*E16</f>
         <v/>
       </c>
@@ -6625,7 +6654,7 @@
         <f>I17*E17</f>
         <v/>
       </c>
-      <c r="K17" s="49">
+      <c r="K17" s="61">
         <f>H17*E17</f>
         <v/>
       </c>
@@ -6678,7 +6707,7 @@
         <f>I18*E18</f>
         <v/>
       </c>
-      <c r="K18" s="49">
+      <c r="K18" s="61">
         <f>H18*E18</f>
         <v/>
       </c>
@@ -6731,7 +6760,7 @@
         <f>I19*E19</f>
         <v/>
       </c>
-      <c r="K19" s="49">
+      <c r="K19" s="61">
         <f>H19*E19</f>
         <v/>
       </c>
@@ -6784,7 +6813,7 @@
         <f>I20*E20</f>
         <v/>
       </c>
-      <c r="K20" s="49">
+      <c r="K20" s="61">
         <f>H20*E20</f>
         <v/>
       </c>
@@ -6844,7 +6873,7 @@
         <f>I22*E22</f>
         <v/>
       </c>
-      <c r="K22" s="49">
+      <c r="K22" s="61">
         <f>H22*E22</f>
         <v/>
       </c>
@@ -6897,7 +6926,7 @@
         <f>I23*E23</f>
         <v/>
       </c>
-      <c r="K23" s="49">
+      <c r="K23" s="61">
         <f>H23*E23</f>
         <v/>
       </c>
@@ -6950,7 +6979,7 @@
         <f>I24*E24</f>
         <v/>
       </c>
-      <c r="K24" s="49">
+      <c r="K24" s="61">
         <f>H24*E24</f>
         <v/>
       </c>
@@ -7003,7 +7032,7 @@
         <f>I25*E25</f>
         <v/>
       </c>
-      <c r="K25" s="49">
+      <c r="K25" s="61">
         <f>H25*E25</f>
         <v/>
       </c>
@@ -7056,7 +7085,7 @@
         <f>I26*E26</f>
         <v/>
       </c>
-      <c r="K26" s="49">
+      <c r="K26" s="61">
         <f>H26*E26</f>
         <v/>
       </c>
@@ -7109,7 +7138,7 @@
         <f>I27*E27</f>
         <v/>
       </c>
-      <c r="K27" s="49">
+      <c r="K27" s="61">
         <f>H27*E27</f>
         <v/>
       </c>
@@ -7125,8 +7154,8 @@
           <t>TỔNG CỘNG CHI PHÍ XÂY LẮP (VNĐ)</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
+      <c r="B28" s="47" t="n"/>
+      <c r="C28" s="48" t="n"/>
       <c r="D28" s="13" t="n"/>
       <c r="E28" s="13" t="n"/>
       <c r="F28" s="29">
@@ -7146,6 +7175,7 @@
       </c>
       <c r="L28" s="13" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30" ht="24" customHeight="1">
       <c r="B30" s="2" t="inlineStr">
         <is>
@@ -7228,7 +7258,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C34" s="50" t="inlineStr">
+      <c r="C34" s="62" t="inlineStr">
         <is>
           <t>SỐ TIỀN THỰC ĐỀ NGHỊ KHO BẠC NHÀ NƯỚC CHUYỂN KỲ NÀY (4 = 1 - 2 - 3)</t>
         </is>
@@ -7246,13 +7276,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="A21:L21"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7399,63 +7422,63 @@
           <t>Tháng 10/2026</t>
         </is>
       </c>
-      <c r="N5" s="51" t="n"/>
-      <c r="O5" s="51" t="n"/>
-      <c r="P5" s="52" t="n"/>
+      <c r="N5" s="49" t="n"/>
+      <c r="O5" s="49" t="n"/>
+      <c r="P5" s="50" t="n"/>
       <c r="Q5" s="39" t="inlineStr">
         <is>
           <t>Tháng 11/2026</t>
         </is>
       </c>
-      <c r="R5" s="51" t="n"/>
-      <c r="S5" s="51" t="n"/>
-      <c r="T5" s="52" t="n"/>
+      <c r="R5" s="49" t="n"/>
+      <c r="S5" s="49" t="n"/>
+      <c r="T5" s="50" t="n"/>
       <c r="U5" s="39" t="inlineStr">
         <is>
           <t>Tháng 12/2026</t>
         </is>
       </c>
-      <c r="V5" s="51" t="n"/>
-      <c r="W5" s="51" t="n"/>
-      <c r="X5" s="52" t="n"/>
+      <c r="V5" s="49" t="n"/>
+      <c r="W5" s="49" t="n"/>
+      <c r="X5" s="50" t="n"/>
       <c r="Y5" s="39" t="inlineStr">
         <is>
           <t>Tháng 01/2027</t>
         </is>
       </c>
-      <c r="Z5" s="51" t="n"/>
-      <c r="AA5" s="51" t="n"/>
-      <c r="AB5" s="52" t="n"/>
+      <c r="Z5" s="49" t="n"/>
+      <c r="AA5" s="49" t="n"/>
+      <c r="AB5" s="50" t="n"/>
       <c r="AC5" s="39" t="inlineStr">
         <is>
           <t>Tháng 02/2027</t>
         </is>
       </c>
-      <c r="AD5" s="51" t="n"/>
-      <c r="AE5" s="51" t="n"/>
-      <c r="AF5" s="52" t="n"/>
+      <c r="AD5" s="49" t="n"/>
+      <c r="AE5" s="49" t="n"/>
+      <c r="AF5" s="50" t="n"/>
       <c r="AG5" s="39" t="inlineStr">
         <is>
           <t>Tháng 03/2027</t>
         </is>
       </c>
-      <c r="AH5" s="51" t="n"/>
-      <c r="AI5" s="51" t="n"/>
-      <c r="AJ5" s="52" t="n"/>
+      <c r="AH5" s="49" t="n"/>
+      <c r="AI5" s="49" t="n"/>
+      <c r="AJ5" s="50" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="53" t="n"/>
-      <c r="B6" s="53" t="n"/>
-      <c r="C6" s="53" t="n"/>
-      <c r="D6" s="53" t="n"/>
-      <c r="E6" s="53" t="n"/>
-      <c r="F6" s="53" t="n"/>
-      <c r="G6" s="53" t="n"/>
-      <c r="H6" s="53" t="n"/>
-      <c r="I6" s="53" t="n"/>
-      <c r="J6" s="53" t="n"/>
-      <c r="K6" s="53" t="n"/>
-      <c r="L6" s="53" t="n"/>
+      <c r="A6" s="51" t="n"/>
+      <c r="B6" s="51" t="n"/>
+      <c r="C6" s="51" t="n"/>
+      <c r="D6" s="51" t="n"/>
+      <c r="E6" s="51" t="n"/>
+      <c r="F6" s="51" t="n"/>
+      <c r="G6" s="51" t="n"/>
+      <c r="H6" s="51" t="n"/>
+      <c r="I6" s="51" t="n"/>
+      <c r="J6" s="51" t="n"/>
+      <c r="K6" s="51" t="n"/>
+      <c r="L6" s="51" t="n"/>
       <c r="M6" s="40" t="inlineStr">
         <is>
           <t>T1</t>
@@ -11014,4 +11037,6293 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:J140"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>DỰ ÁN: CAO TỐC TUYÊN QUANG - HÀ GIANG (GIAI ĐOẠN 1) - CẦU KM19+529.080</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>BẢNG PHÂN TÍCH ĐỊNH MỨC HAO PHÍ VẬT LIỆU CHO TỪNG HẠNG MỤC CÔNG TÁC WBS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Chi tiết sắt thép từng loại đường kính Ø, xi măng, cát, đá, cáp DƯL (Theo Định mức Thông tư 12/2021/TT-BXD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Mã định mức</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Hạng mục công tác WBS</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Khối lượng công tác</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>ĐVT công tác</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Tên quy cách vật tư cấu thành</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>ĐVT vật tư</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Định mức cho 1 ĐVT</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Hao phí vật tư hạng mục</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Tiêu chuẩn kỹ thuật áp dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>AC.11111</t>
+        </is>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>Khoan tạo lỗ cọc khoan nhồi D1200mm (26 cọc L=20m-40m)</t>
+        </is>
+      </c>
+      <c r="D6" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J7</f>
+        <v/>
+      </c>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F6" s="55" t="n"/>
+      <c r="G6" s="55" t="n"/>
+      <c r="H6" s="55" t="n"/>
+      <c r="I6" s="55" t="n"/>
+      <c r="J6" s="55" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Bột sét Bentonite tạo vách khoan</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>Bột sét Bentonite tạo vách khoan</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H7" s="56" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I7" s="42">
+        <f>D6*H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 9395:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch thi công khoan cọc</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch thi công khoan cọc</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H8" s="56" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I8" s="42">
+        <f>D6*H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>AC.12111</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>Hạ và nhổ ống vách thép dẫn hướng D1300mm d=8mm</t>
+        </is>
+      </c>
+      <c r="D9" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J12</f>
+        <v/>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F9" s="55" t="n"/>
+      <c r="G9" s="55" t="n"/>
+      <c r="H9" s="55" t="n"/>
+      <c r="I9" s="55" t="n"/>
+      <c r="J9" s="55" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Ống vách thép dẫn hướng D1300 d=8mm (khấu hao)</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>Ống vách thép dẫn hướng D1300 d=8mm (khấu hao)</t>
+        </is>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H10" s="56" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="I10" s="42">
+        <f>D9*H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 9395:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="52" t="inlineStr">
+        <is>
+          <t>AF.21111</t>
+        </is>
+      </c>
+      <c r="C11" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông cọc khoan nhồi C30/37 đổ bằng ống Tremie</t>
+        </is>
+      </c>
+      <c r="D11" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J17</f>
+        <v/>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="n"/>
+      <c r="G11" s="55" t="n"/>
+      <c r="H11" s="55" t="n"/>
+      <c r="I11" s="55" t="n"/>
+      <c r="J11" s="55" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 cọc khoan nhồi</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 cọc khoan nhồi</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>395</v>
+      </c>
+      <c r="I12" s="42">
+        <f>D11*H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng hạt trung Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng hạt trung Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H13" s="56" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I13" s="42">
+        <f>D11*H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch chọn lọc</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch chọn lọc</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H14" s="56" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I14" s="42">
+        <f>D11*H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H15" s="42" t="n">
+        <v>185</v>
+      </c>
+      <c r="I15" s="42">
+        <f>D11*H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia hoá dẻo chậm đông kết</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia hoá dẻo chậm đông kết</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I16" s="42">
+        <f>D11*H16</f>
+        <v/>
+      </c>
+      <c r="J16" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type G</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="52" t="inlineStr">
+        <is>
+          <t>AF.61111</t>
+        </is>
+      </c>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>Cốt thép cọc khoan nhồi D1200mm (Lồng thép)</t>
+        </is>
+      </c>
+      <c r="D17" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J22</f>
+        <v/>
+      </c>
+      <c r="E17" s="52" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="F17" s="55" t="n"/>
+      <c r="G17" s="55" t="n"/>
+      <c r="H17" s="55" t="n"/>
+      <c r="I17" s="55" t="n"/>
+      <c r="J17" s="55" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="n"/>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép chủ cọc nhồi vằn Ø25 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>Thép chủ cọc nhồi vằn Ø25 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H18" s="56" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="I18" s="42">
+        <f>D17*H18</f>
+        <v/>
+      </c>
+      <c r="J18" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép đai tăng cường vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <t>Thép đai tăng cường vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H19" s="56" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I19" s="42">
+        <f>D17*H19</f>
+        <v/>
+      </c>
+      <c r="J19" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép đai xoắn liên tục tròn trơn Ø10 (CB240-T)</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>Thép đai xoắn liên tục tròn trơn Ø10 (CB240-T)</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H20" s="56" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="I20" s="42">
+        <f>D17*H20</f>
+        <v/>
+      </c>
+      <c r="J20" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Ống siêu âm cọc nhồi thép Ø60x2</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="30" t="inlineStr">
+        <is>
+          <t>Ống siêu âm cọc nhồi thép Ø60x2</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H21" s="42" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I21" s="42">
+        <f>D17*H21</f>
+        <v/>
+      </c>
+      <c r="J21" s="30" t="inlineStr">
+        <is>
+          <t>ASTM A53 / TCVN 9395</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Dây thép buộc 1 ly</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <t>Dây thép buộc 1 ly</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H22" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" s="42">
+        <f>D17*H22</f>
+        <v/>
+      </c>
+      <c r="J22" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Que hàn điện E42/E50</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="30" t="inlineStr">
+        <is>
+          <t>Que hàn điện E42/E50</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H23" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="42">
+        <f>D17*H23</f>
+        <v/>
+      </c>
+      <c r="J23" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 3223:2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>AF.11111</t>
+        </is>
+      </c>
+      <c r="C24" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông lót đáy bệ móng mác C10 dày 10cm</t>
+        </is>
+      </c>
+      <c r="D24" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J34</f>
+        <v/>
+      </c>
+      <c r="E24" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F24" s="55" t="n"/>
+      <c r="G24" s="55" t="n"/>
+      <c r="H24" s="55" t="n"/>
+      <c r="I24" s="55" t="n"/>
+      <c r="J24" s="55" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 lót móng</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 lót móng</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H25" s="42" t="n">
+        <v>240</v>
+      </c>
+      <c r="I25" s="42">
+        <f>D24*H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng xây dựng</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng xây dựng</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H26" s="56" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I26" s="42">
+        <f>D24*H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2</t>
+        </is>
+      </c>
+      <c r="G27" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H27" s="56" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I27" s="42">
+        <f>D24*H27</f>
+        <v/>
+      </c>
+      <c r="J27" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="n"/>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G28" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H28" s="42" t="n">
+        <v>175</v>
+      </c>
+      <c r="I28" s="42">
+        <f>D24*H28</f>
+        <v/>
+      </c>
+      <c r="J28" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="52" t="inlineStr">
+        <is>
+          <t>AF.12111</t>
+        </is>
+      </c>
+      <c r="C29" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông bệ móng mố M1, M2 và bệ trụ T1, T2 mác C30</t>
+        </is>
+      </c>
+      <c r="D29" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J39</f>
+        <v/>
+      </c>
+      <c r="E29" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F29" s="55" t="n"/>
+      <c r="G29" s="55" t="n"/>
+      <c r="H29" s="55" t="n"/>
+      <c r="I29" s="55" t="n"/>
+      <c r="J29" s="55" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 bệ móng</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 bệ móng</t>
+        </is>
+      </c>
+      <c r="G30" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H30" s="42" t="n">
+        <v>385</v>
+      </c>
+      <c r="I30" s="42">
+        <f>D29*H30</f>
+        <v/>
+      </c>
+      <c r="J30" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G31" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H31" s="56" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I31" s="42">
+        <f>D29*H31</f>
+        <v/>
+      </c>
+      <c r="J31" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="n"/>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H32" s="56" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I32" s="42">
+        <f>D29*H32</f>
+        <v/>
+      </c>
+      <c r="J32" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H33" s="42" t="n">
+        <v>180</v>
+      </c>
+      <c r="I33" s="42">
+        <f>D29*H33</f>
+        <v/>
+      </c>
+      <c r="J33" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="n"/>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H34" s="42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I34" s="42">
+        <f>D29*H34</f>
+        <v/>
+      </c>
+      <c r="J34" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="52" t="inlineStr">
+        <is>
+          <t>AF.12211</t>
+        </is>
+      </c>
+      <c r="C35" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông thân mố chân dê M1 và mố chữ U M2 mác C30</t>
+        </is>
+      </c>
+      <c r="D35" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J44</f>
+        <v/>
+      </c>
+      <c r="E35" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F35" s="55" t="n"/>
+      <c r="G35" s="55" t="n"/>
+      <c r="H35" s="55" t="n"/>
+      <c r="I35" s="55" t="n"/>
+      <c r="J35" s="55" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="n"/>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 thân mố</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 thân mố</t>
+        </is>
+      </c>
+      <c r="G36" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H36" s="42" t="n">
+        <v>385</v>
+      </c>
+      <c r="I36" s="42">
+        <f>D35*H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="n"/>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H37" s="56" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I37" s="42">
+        <f>D35*H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="G38" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H38" s="56" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I38" s="42">
+        <f>D35*H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="19" t="n"/>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H39" s="42" t="n">
+        <v>180</v>
+      </c>
+      <c r="I39" s="42">
+        <f>D35*H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="19" t="n"/>
+      <c r="F40" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H40" s="42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I40" s="42">
+        <f>D35*H40</f>
+        <v/>
+      </c>
+      <c r="J40" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" s="52" t="inlineStr">
+        <is>
+          <t>AF.12311</t>
+        </is>
+      </c>
+      <c r="C41" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông tường cánh và tường đỉnh mố M1, M2 mác C30</t>
+        </is>
+      </c>
+      <c r="D41" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J47</f>
+        <v/>
+      </c>
+      <c r="E41" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F41" s="55" t="n"/>
+      <c r="G41" s="55" t="n"/>
+      <c r="H41" s="55" t="n"/>
+      <c r="I41" s="55" t="n"/>
+      <c r="J41" s="55" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 tường cánh</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 tường cánh</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H42" s="42" t="n">
+        <v>385</v>
+      </c>
+      <c r="I42" s="42">
+        <f>D41*H42</f>
+        <v/>
+      </c>
+      <c r="J42" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="n"/>
+      <c r="B43" s="19" t="n"/>
+      <c r="C43" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="n"/>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G43" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H43" s="56" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I43" s="42">
+        <f>D41*H43</f>
+        <v/>
+      </c>
+      <c r="J43" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="n"/>
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="G44" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H44" s="56" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I44" s="42">
+        <f>D41*H44</f>
+        <v/>
+      </c>
+      <c r="J44" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="n"/>
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G45" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H45" s="42" t="n">
+        <v>180</v>
+      </c>
+      <c r="I45" s="42">
+        <f>D41*H45</f>
+        <v/>
+      </c>
+      <c r="J45" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="n"/>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="G46" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H46" s="42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I46" s="42">
+        <f>D41*H46</f>
+        <v/>
+      </c>
+      <c r="J46" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="52" t="n">
+        <v>9</v>
+      </c>
+      <c r="B47" s="52" t="inlineStr">
+        <is>
+          <t>AF.13111</t>
+        </is>
+      </c>
+      <c r="C47" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông thân đặc trụ T1 và T2 mác C30</t>
+        </is>
+      </c>
+      <c r="D47" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J50</f>
+        <v/>
+      </c>
+      <c r="E47" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F47" s="55" t="n"/>
+      <c r="G47" s="55" t="n"/>
+      <c r="H47" s="55" t="n"/>
+      <c r="I47" s="55" t="n"/>
+      <c r="J47" s="55" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="n"/>
+      <c r="B48" s="19" t="n"/>
+      <c r="C48" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 thân trụ</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 thân trụ</t>
+        </is>
+      </c>
+      <c r="G48" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H48" s="42" t="n">
+        <v>385</v>
+      </c>
+      <c r="I48" s="42">
+        <f>D47*H48</f>
+        <v/>
+      </c>
+      <c r="J48" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="n"/>
+      <c r="B49" s="19" t="n"/>
+      <c r="C49" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="n"/>
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G49" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H49" s="56" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I49" s="42">
+        <f>D47*H49</f>
+        <v/>
+      </c>
+      <c r="J49" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="n"/>
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="n"/>
+      <c r="E50" s="19" t="n"/>
+      <c r="F50" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="G50" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H50" s="56" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I50" s="42">
+        <f>D47*H50</f>
+        <v/>
+      </c>
+      <c r="J50" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="n"/>
+      <c r="B51" s="19" t="n"/>
+      <c r="C51" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G51" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H51" s="42" t="n">
+        <v>180</v>
+      </c>
+      <c r="I51" s="42">
+        <f>D47*H51</f>
+        <v/>
+      </c>
+      <c r="J51" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="n"/>
+      <c r="B52" s="19" t="n"/>
+      <c r="C52" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="G52" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H52" s="42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I52" s="42">
+        <f>D47*H52</f>
+        <v/>
+      </c>
+      <c r="J52" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="B53" s="52" t="inlineStr">
+        <is>
+          <t>AF.13211</t>
+        </is>
+      </c>
+      <c r="C53" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông xà mũ trụ T1, T2 mác C35</t>
+        </is>
+      </c>
+      <c r="D53" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J53</f>
+        <v/>
+      </c>
+      <c r="E53" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F53" s="55" t="n"/>
+      <c r="G53" s="55" t="n"/>
+      <c r="H53" s="55" t="n"/>
+      <c r="I53" s="55" t="n"/>
+      <c r="J53" s="55" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="n"/>
+      <c r="B54" s="19" t="n"/>
+      <c r="C54" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 xà mũ trụ</t>
+        </is>
+      </c>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 xà mũ trụ</t>
+        </is>
+      </c>
+      <c r="G54" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H54" s="42" t="n">
+        <v>425</v>
+      </c>
+      <c r="I54" s="42">
+        <f>D53*H54</f>
+        <v/>
+      </c>
+      <c r="J54" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="n"/>
+      <c r="B55" s="19" t="n"/>
+      <c r="C55" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G55" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H55" s="56" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I55" s="42">
+        <f>D53*H55</f>
+        <v/>
+      </c>
+      <c r="J55" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="n"/>
+      <c r="B56" s="19" t="n"/>
+      <c r="C56" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch chọn lọc</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch chọn lọc</t>
+        </is>
+      </c>
+      <c r="G56" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H56" s="56" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I56" s="42">
+        <f>D53*H56</f>
+        <v/>
+      </c>
+      <c r="J56" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="n"/>
+      <c r="B57" s="19" t="n"/>
+      <c r="C57" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G57" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H57" s="42" t="n">
+        <v>180</v>
+      </c>
+      <c r="I57" s="42">
+        <f>D53*H57</f>
+        <v/>
+      </c>
+      <c r="J57" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="n"/>
+      <c r="B58" s="19" t="n"/>
+      <c r="C58" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="G58" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H58" s="42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I58" s="42">
+        <f>D53*H58</f>
+        <v/>
+      </c>
+      <c r="J58" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="B59" s="52" t="inlineStr">
+        <is>
+          <t>AF.62111</t>
+        </is>
+      </c>
+      <c r="C59" s="53" t="inlineStr">
+        <is>
+          <t>Cốt thép mố và trụ (Bệ móng, Thân mố, Thân trụ, Xà mũ)</t>
+        </is>
+      </c>
+      <c r="D59" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J56</f>
+        <v/>
+      </c>
+      <c r="E59" s="52" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="F59" s="55" t="n"/>
+      <c r="G59" s="55" t="n"/>
+      <c r="H59" s="55" t="n"/>
+      <c r="I59" s="55" t="n"/>
+      <c r="J59" s="55" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="n"/>
+      <c r="B60" s="19" t="n"/>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép lưới đáy bệ móng vằn Ø32 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>Thép lưới đáy bệ móng vằn Ø32 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="G60" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H60" s="56" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="I60" s="42">
+        <f>D59*H60</f>
+        <v/>
+      </c>
+      <c r="J60" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="n"/>
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép đứng thân trụ vằn Ø32 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="30" t="inlineStr">
+        <is>
+          <t>Thép đứng thân trụ vằn Ø32 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="G61" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H61" s="56" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="I61" s="42">
+        <f>D59*H61</f>
+        <v/>
+      </c>
+      <c r="J61" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="19" t="n"/>
+      <c r="B62" s="19" t="n"/>
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép đứng thân mố vằn Ø28 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>Thép đứng thân mố vằn Ø28 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="G62" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H62" s="56" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="I62" s="42">
+        <f>D59*H62</f>
+        <v/>
+      </c>
+      <c r="J62" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="19" t="n"/>
+      <c r="B63" s="19" t="n"/>
+      <c r="C63" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép xà mũ chịu uốn vằn Ø28 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="30" t="inlineStr">
+        <is>
+          <t>Thép xà mũ chịu uốn vằn Ø28 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="G63" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H63" s="56" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="I63" s="42">
+        <f>D59*H63</f>
+        <v/>
+      </c>
+      <c r="J63" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="19" t="n"/>
+      <c r="B64" s="19" t="n"/>
+      <c r="C64" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép phân bố bệ móng vằn Ø20 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="30" t="inlineStr">
+        <is>
+          <t>Thép phân bố bệ móng vằn Ø20 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="G64" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H64" s="56" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I64" s="42">
+        <f>D59*H64</f>
+        <v/>
+      </c>
+      <c r="J64" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n"/>
+      <c r="B65" s="19" t="n"/>
+      <c r="C65" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép đai mố trụ vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="n"/>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="30" t="inlineStr">
+        <is>
+          <t>Thép đai mố trụ vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="G65" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H65" s="56" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I65" s="42">
+        <f>D59*H65</f>
+        <v/>
+      </c>
+      <c r="J65" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n"/>
+      <c r="B66" s="19" t="n"/>
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép đai cấu tạo tròn trơn Ø10 (CB240-T)</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="30" t="inlineStr">
+        <is>
+          <t>Thép đai cấu tạo tròn trơn Ø10 (CB240-T)</t>
+        </is>
+      </c>
+      <c r="G66" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H66" s="56" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I66" s="42">
+        <f>D59*H66</f>
+        <v/>
+      </c>
+      <c r="J66" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="19" t="n"/>
+      <c r="B67" s="19" t="n"/>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Dây thép buộc 1 ly</t>
+        </is>
+      </c>
+      <c r="D67" s="19" t="n"/>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>Dây thép buộc 1 ly</t>
+        </is>
+      </c>
+      <c r="G67" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H67" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="I67" s="42">
+        <f>D59*H67</f>
+        <v/>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="19" t="n"/>
+      <c r="B68" s="19" t="n"/>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Que hàn điện E42/E50</t>
+        </is>
+      </c>
+      <c r="D68" s="19" t="n"/>
+      <c r="E68" s="19" t="n"/>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>Que hàn điện E42/E50</t>
+        </is>
+      </c>
+      <c r="G68" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H68" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="I68" s="42">
+        <f>D59*H68</f>
+        <v/>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 3223:2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="52" t="n">
+        <v>12</v>
+      </c>
+      <c r="B69" s="52" t="inlineStr">
+        <is>
+          <t>AF.31111</t>
+        </is>
+      </c>
+      <c r="C69" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông dầm chủ Super-T L=38.2m mác C45 (15 phiến)</t>
+        </is>
+      </c>
+      <c r="D69" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J62</f>
+        <v/>
+      </c>
+      <c r="E69" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F69" s="55" t="n"/>
+      <c r="G69" s="55" t="n"/>
+      <c r="H69" s="55" t="n"/>
+      <c r="I69" s="55" t="n"/>
+      <c r="J69" s="55" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="n"/>
+      <c r="B70" s="19" t="n"/>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 dầm Super-T</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="n"/>
+      <c r="E70" s="19" t="n"/>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 dầm Super-T</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H70" s="42" t="n">
+        <v>485</v>
+      </c>
+      <c r="I70" s="42">
+        <f>D69*H70</f>
+        <v/>
+      </c>
+      <c r="J70" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19" t="n"/>
+      <c r="B71" s="19" t="n"/>
+      <c r="C71" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng chọn lọc thô Mk&gt;=2.6</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="n"/>
+      <c r="E71" s="19" t="n"/>
+      <c r="F71" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng chọn lọc thô Mk&gt;=2.6</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H71" s="56" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I71" s="42">
+        <f>D69*H71</f>
+        <v/>
+      </c>
+      <c r="J71" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="19" t="n"/>
+      <c r="B72" s="19" t="n"/>
+      <c r="C72" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 nghiền rửa chọn lọc</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="n"/>
+      <c r="E72" s="19" t="n"/>
+      <c r="F72" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 nghiền rửa chọn lọc</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H72" s="56" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I72" s="42">
+        <f>D69*H72</f>
+        <v/>
+      </c>
+      <c r="J72" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="19" t="n"/>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D73" s="19" t="n"/>
+      <c r="E73" s="19" t="n"/>
+      <c r="F73" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H73" s="42" t="n">
+        <v>165</v>
+      </c>
+      <c r="I73" s="42">
+        <f>D69*H73</f>
+        <v/>
+      </c>
+      <c r="J73" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="19" t="n"/>
+      <c r="B74" s="19" t="n"/>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia siêu dẻo Polycarboxylate thế hệ 3</t>
+        </is>
+      </c>
+      <c r="D74" s="19" t="n"/>
+      <c r="E74" s="19" t="n"/>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo Polycarboxylate thế hệ 3</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H74" s="42" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I74" s="42">
+        <f>D69*H74</f>
+        <v/>
+      </c>
+      <c r="J74" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="52" t="n">
+        <v>13</v>
+      </c>
+      <c r="B75" s="52" t="inlineStr">
+        <is>
+          <t>AF.63111</t>
+        </is>
+      </c>
+      <c r="C75" s="53" t="inlineStr">
+        <is>
+          <t>Cáp dự ứng lực tao xoắn 15.2mm Grade 270 dầm Super-T</t>
+        </is>
+      </c>
+      <c r="D75" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J64</f>
+        <v/>
+      </c>
+      <c r="E75" s="52" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="F75" s="55" t="n"/>
+      <c r="G75" s="55" t="n"/>
+      <c r="H75" s="55" t="n"/>
+      <c r="I75" s="55" t="n"/>
+      <c r="J75" s="55" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="19" t="n"/>
+      <c r="B76" s="19" t="n"/>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cáp dự ứng lực tao 15.2mm Gr270</t>
+        </is>
+      </c>
+      <c r="D76" s="19" t="n"/>
+      <c r="E76" s="19" t="n"/>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>Cáp dự ứng lực tao 15.2mm Gr270</t>
+        </is>
+      </c>
+      <c r="G76" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H76" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="42">
+        <f>D75*H76</f>
+        <v/>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>ASTM A416 / TCVN 11823</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="19" t="n"/>
+      <c r="B77" s="19" t="n"/>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Bộ neo chùm dự ứng lực (12 bộ/phiến dầm)</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="n"/>
+      <c r="E77" s="19" t="n"/>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>Bộ neo chùm dự ứng lực (12 bộ/phiến dầm)</t>
+        </is>
+      </c>
+      <c r="G77" s="31" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="H77" s="42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I77" s="42">
+        <f>D75*H77</f>
+        <v/>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="19" t="n"/>
+      <c r="B78" s="19" t="n"/>
+      <c r="C78" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Ống ghen tôn mạ kẽm luồn cáp DƯL</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="n"/>
+      <c r="E78" s="19" t="n"/>
+      <c r="F78" s="30" t="inlineStr">
+        <is>
+          <t>Ống ghen tôn mạ kẽm luồn cáp DƯL</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H78" s="42" t="n">
+        <v>36</v>
+      </c>
+      <c r="I78" s="42">
+        <f>D75*H78</f>
+        <v/>
+      </c>
+      <c r="J78" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="19" t="n"/>
+      <c r="B79" s="19" t="n"/>
+      <c r="C79" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Vữa không co ngót bơm lấp ống ghen SikaGrout</t>
+        </is>
+      </c>
+      <c r="D79" s="19" t="n"/>
+      <c r="E79" s="19" t="n"/>
+      <c r="F79" s="30" t="inlineStr">
+        <is>
+          <t>Vữa không co ngót bơm lấp ống ghen SikaGrout</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H79" s="42" t="n">
+        <v>380</v>
+      </c>
+      <c r="I79" s="42">
+        <f>D75*H79</f>
+        <v/>
+      </c>
+      <c r="J79" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C1107</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="52" t="n">
+        <v>14</v>
+      </c>
+      <c r="B80" s="52" t="inlineStr">
+        <is>
+          <t>AF.64111</t>
+        </is>
+      </c>
+      <c r="C80" s="53" t="inlineStr">
+        <is>
+          <t>Cốt thép thường dầm chủ Super-T (Thép sườn, cánh)</t>
+        </is>
+      </c>
+      <c r="D80" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J66</f>
+        <v/>
+      </c>
+      <c r="E80" s="52" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="F80" s="55" t="n"/>
+      <c r="G80" s="55" t="n"/>
+      <c r="H80" s="55" t="n"/>
+      <c r="I80" s="55" t="n"/>
+      <c r="J80" s="55" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="19" t="n"/>
+      <c r="B81" s="19" t="n"/>
+      <c r="C81" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép sườn dầm Super-T vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="D81" s="19" t="n"/>
+      <c r="E81" s="19" t="n"/>
+      <c r="F81" s="30" t="inlineStr">
+        <is>
+          <t>Thép sườn dầm Super-T vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H81" s="56" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I81" s="42">
+        <f>D80*H81</f>
+        <v/>
+      </c>
+      <c r="J81" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="19" t="n"/>
+      <c r="B82" s="19" t="n"/>
+      <c r="C82" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép bản cánh dầm Super-T vằn Ø14 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="D82" s="19" t="n"/>
+      <c r="E82" s="19" t="n"/>
+      <c r="F82" s="30" t="inlineStr">
+        <is>
+          <t>Thép bản cánh dầm Super-T vằn Ø14 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H82" s="56" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I82" s="42">
+        <f>D80*H82</f>
+        <v/>
+      </c>
+      <c r="J82" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="n"/>
+      <c r="B83" s="19" t="n"/>
+      <c r="C83" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép đai và móc cẩu dầm tròn trơn Ø10 (CB240-T)</t>
+        </is>
+      </c>
+      <c r="D83" s="19" t="n"/>
+      <c r="E83" s="19" t="n"/>
+      <c r="F83" s="30" t="inlineStr">
+        <is>
+          <t>Thép đai và móc cẩu dầm tròn trơn Ø10 (CB240-T)</t>
+        </is>
+      </c>
+      <c r="G83" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H83" s="56" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I83" s="42">
+        <f>D80*H83</f>
+        <v/>
+      </c>
+      <c r="J83" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="n"/>
+      <c r="B84" s="19" t="n"/>
+      <c r="C84" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Dây thép buộc 1 ly</t>
+        </is>
+      </c>
+      <c r="D84" s="19" t="n"/>
+      <c r="E84" s="19" t="n"/>
+      <c r="F84" s="30" t="inlineStr">
+        <is>
+          <t>Dây thép buộc 1 ly</t>
+        </is>
+      </c>
+      <c r="G84" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H84" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="I84" s="42">
+        <f>D80*H84</f>
+        <v/>
+      </c>
+      <c r="J84" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="52" t="n">
+        <v>15</v>
+      </c>
+      <c r="B85" s="52" t="inlineStr">
+        <is>
+          <t>AF.32111</t>
+        </is>
+      </c>
+      <c r="C85" s="53" t="inlineStr">
+        <is>
+          <t>Gối chậu cao su di động đơn hướng &amp; cố định</t>
+        </is>
+      </c>
+      <c r="D85" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J70</f>
+        <v/>
+      </c>
+      <c r="E85" s="52" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="F85" s="55" t="n"/>
+      <c r="G85" s="55" t="n"/>
+      <c r="H85" s="55" t="n"/>
+      <c r="I85" s="55" t="n"/>
+      <c r="J85" s="55" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="19" t="n"/>
+      <c r="B86" s="19" t="n"/>
+      <c r="C86" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Gối chậu cao su cốt bản thép chịu lực</t>
+        </is>
+      </c>
+      <c r="D86" s="19" t="n"/>
+      <c r="E86" s="19" t="n"/>
+      <c r="F86" s="30" t="inlineStr">
+        <is>
+          <t>Gối chậu cao su cốt bản thép chịu lực</t>
+        </is>
+      </c>
+      <c r="G86" s="31" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="H86" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="42">
+        <f>D85*H86</f>
+        <v/>
+      </c>
+      <c r="J86" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017 / AASHTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="52" t="n">
+        <v>16</v>
+      </c>
+      <c r="B87" s="52" t="inlineStr">
+        <is>
+          <t>AF.33111</t>
+        </is>
+      </c>
+      <c r="C87" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông dầm ngang mố và trụ mác C35</t>
+        </is>
+      </c>
+      <c r="D87" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J73</f>
+        <v/>
+      </c>
+      <c r="E87" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F87" s="55" t="n"/>
+      <c r="G87" s="55" t="n"/>
+      <c r="H87" s="55" t="n"/>
+      <c r="I87" s="55" t="n"/>
+      <c r="J87" s="55" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="19" t="n"/>
+      <c r="B88" s="19" t="n"/>
+      <c r="C88" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 dầm ngang</t>
+        </is>
+      </c>
+      <c r="D88" s="19" t="n"/>
+      <c r="E88" s="19" t="n"/>
+      <c r="F88" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 dầm ngang</t>
+        </is>
+      </c>
+      <c r="G88" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H88" s="42" t="n">
+        <v>420</v>
+      </c>
+      <c r="I88" s="42">
+        <f>D87*H88</f>
+        <v/>
+      </c>
+      <c r="J88" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="19" t="n"/>
+      <c r="B89" s="19" t="n"/>
+      <c r="C89" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="n"/>
+      <c r="E89" s="19" t="n"/>
+      <c r="F89" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G89" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H89" s="56" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I89" s="42">
+        <f>D87*H89</f>
+        <v/>
+      </c>
+      <c r="J89" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="19" t="n"/>
+      <c r="B90" s="19" t="n"/>
+      <c r="C90" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="D90" s="19" t="n"/>
+      <c r="E90" s="19" t="n"/>
+      <c r="F90" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="G90" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H90" s="56" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I90" s="42">
+        <f>D87*H90</f>
+        <v/>
+      </c>
+      <c r="J90" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="19" t="n"/>
+      <c r="B91" s="19" t="n"/>
+      <c r="C91" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D91" s="19" t="n"/>
+      <c r="E91" s="19" t="n"/>
+      <c r="F91" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G91" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H91" s="42" t="n">
+        <v>180</v>
+      </c>
+      <c r="I91" s="42">
+        <f>D87*H91</f>
+        <v/>
+      </c>
+      <c r="J91" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="19" t="n"/>
+      <c r="B92" s="19" t="n"/>
+      <c r="C92" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="D92" s="19" t="n"/>
+      <c r="E92" s="19" t="n"/>
+      <c r="F92" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="G92" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H92" s="42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I92" s="42">
+        <f>D87*H92</f>
+        <v/>
+      </c>
+      <c r="J92" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="52" t="n">
+        <v>17</v>
+      </c>
+      <c r="B93" s="52" t="inlineStr">
+        <is>
+          <t>AF.35111</t>
+        </is>
+      </c>
+      <c r="C93" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông bản mặt cầu đổ tại chỗ dày 20cm mác C35</t>
+        </is>
+      </c>
+      <c r="D93" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J77</f>
+        <v/>
+      </c>
+      <c r="E93" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F93" s="55" t="n"/>
+      <c r="G93" s="55" t="n"/>
+      <c r="H93" s="55" t="n"/>
+      <c r="I93" s="55" t="n"/>
+      <c r="J93" s="55" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="19" t="n"/>
+      <c r="B94" s="19" t="n"/>
+      <c r="C94" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 bản mặt cầu</t>
+        </is>
+      </c>
+      <c r="D94" s="19" t="n"/>
+      <c r="E94" s="19" t="n"/>
+      <c r="F94" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 bản mặt cầu</t>
+        </is>
+      </c>
+      <c r="G94" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H94" s="42" t="n">
+        <v>420</v>
+      </c>
+      <c r="I94" s="42">
+        <f>D93*H94</f>
+        <v/>
+      </c>
+      <c r="J94" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="19" t="n"/>
+      <c r="B95" s="19" t="n"/>
+      <c r="C95" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="n"/>
+      <c r="E95" s="19" t="n"/>
+      <c r="F95" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G95" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H95" s="56" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I95" s="42">
+        <f>D93*H95</f>
+        <v/>
+      </c>
+      <c r="J95" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="19" t="n"/>
+      <c r="B96" s="19" t="n"/>
+      <c r="C96" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="D96" s="19" t="n"/>
+      <c r="E96" s="19" t="n"/>
+      <c r="F96" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="G96" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H96" s="56" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I96" s="42">
+        <f>D93*H96</f>
+        <v/>
+      </c>
+      <c r="J96" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="19" t="n"/>
+      <c r="B97" s="19" t="n"/>
+      <c r="C97" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="n"/>
+      <c r="E97" s="19" t="n"/>
+      <c r="F97" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G97" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H97" s="42" t="n">
+        <v>180</v>
+      </c>
+      <c r="I97" s="42">
+        <f>D93*H97</f>
+        <v/>
+      </c>
+      <c r="J97" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="19" t="n"/>
+      <c r="B98" s="19" t="n"/>
+      <c r="C98" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="D98" s="19" t="n"/>
+      <c r="E98" s="19" t="n"/>
+      <c r="F98" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="G98" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H98" s="42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I98" s="42">
+        <f>D93*H98</f>
+        <v/>
+      </c>
+      <c r="J98" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="B99" s="52" t="inlineStr">
+        <is>
+          <t>AF.36111</t>
+        </is>
+      </c>
+      <c r="C99" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông mối nối liên tục nhiệt đỉnh trụ T1, T2 mác C35</t>
+        </is>
+      </c>
+      <c r="D99" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J79</f>
+        <v/>
+      </c>
+      <c r="E99" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F99" s="55" t="n"/>
+      <c r="G99" s="55" t="n"/>
+      <c r="H99" s="55" t="n"/>
+      <c r="I99" s="55" t="n"/>
+      <c r="J99" s="55" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="19" t="n"/>
+      <c r="B100" s="19" t="n"/>
+      <c r="C100" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 liên tục nhiệt</t>
+        </is>
+      </c>
+      <c r="D100" s="19" t="n"/>
+      <c r="E100" s="19" t="n"/>
+      <c r="F100" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 liên tục nhiệt</t>
+        </is>
+      </c>
+      <c r="G100" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H100" s="42" t="n">
+        <v>420</v>
+      </c>
+      <c r="I100" s="42">
+        <f>D99*H100</f>
+        <v/>
+      </c>
+      <c r="J100" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="n"/>
+      <c r="B101" s="19" t="n"/>
+      <c r="C101" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D101" s="19" t="n"/>
+      <c r="E101" s="19" t="n"/>
+      <c r="F101" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G101" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H101" s="56" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I101" s="42">
+        <f>D99*H101</f>
+        <v/>
+      </c>
+      <c r="J101" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="19" t="n"/>
+      <c r="B102" s="19" t="n"/>
+      <c r="C102" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="D102" s="19" t="n"/>
+      <c r="E102" s="19" t="n"/>
+      <c r="F102" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="G102" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H102" s="56" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I102" s="42">
+        <f>D99*H102</f>
+        <v/>
+      </c>
+      <c r="J102" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="19" t="n"/>
+      <c r="B103" s="19" t="n"/>
+      <c r="C103" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D103" s="19" t="n"/>
+      <c r="E103" s="19" t="n"/>
+      <c r="F103" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G103" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H103" s="42" t="n">
+        <v>180</v>
+      </c>
+      <c r="I103" s="42">
+        <f>D99*H103</f>
+        <v/>
+      </c>
+      <c r="J103" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="19" t="n"/>
+      <c r="B104" s="19" t="n"/>
+      <c r="C104" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="D104" s="19" t="n"/>
+      <c r="E104" s="19" t="n"/>
+      <c r="F104" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo giảm nước</t>
+        </is>
+      </c>
+      <c r="G104" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H104" s="42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I104" s="42">
+        <f>D99*H104</f>
+        <v/>
+      </c>
+      <c r="J104" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="B105" s="52" t="inlineStr">
+        <is>
+          <t>AF.65111</t>
+        </is>
+      </c>
+      <c r="C105" s="53" t="inlineStr">
+        <is>
+          <t>Cốt thép bản mặt cầu và mối nối liên tục nhiệt</t>
+        </is>
+      </c>
+      <c r="D105" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J81</f>
+        <v/>
+      </c>
+      <c r="E105" s="52" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="F105" s="55" t="n"/>
+      <c r="G105" s="55" t="n"/>
+      <c r="H105" s="55" t="n"/>
+      <c r="I105" s="55" t="n"/>
+      <c r="J105" s="55" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="n"/>
+      <c r="B106" s="19" t="n"/>
+      <c r="C106" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép bản mặt cầu chịu lực lưới dưới vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="D106" s="19" t="n"/>
+      <c r="E106" s="19" t="n"/>
+      <c r="F106" s="30" t="inlineStr">
+        <is>
+          <t>Thép bản mặt cầu chịu lực lưới dưới vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="G106" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H106" s="56" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I106" s="42">
+        <f>D105*H106</f>
+        <v/>
+      </c>
+      <c r="J106" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="19" t="n"/>
+      <c r="B107" s="19" t="n"/>
+      <c r="C107" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép bản mặt cầu lưới trên vằn Ø14 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="D107" s="19" t="n"/>
+      <c r="E107" s="19" t="n"/>
+      <c r="F107" s="30" t="inlineStr">
+        <is>
+          <t>Thép bản mặt cầu lưới trên vằn Ø14 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="G107" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H107" s="56" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I107" s="42">
+        <f>D105*H107</f>
+        <v/>
+      </c>
+      <c r="J107" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="n"/>
+      <c r="B108" s="19" t="n"/>
+      <c r="C108" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép đai chống nứt tròn trơn Ø10 (CB240-T)</t>
+        </is>
+      </c>
+      <c r="D108" s="19" t="n"/>
+      <c r="E108" s="19" t="n"/>
+      <c r="F108" s="30" t="inlineStr">
+        <is>
+          <t>Thép đai chống nứt tròn trơn Ø10 (CB240-T)</t>
+        </is>
+      </c>
+      <c r="G108" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H108" s="56" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I108" s="42">
+        <f>D105*H108</f>
+        <v/>
+      </c>
+      <c r="J108" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="19" t="n"/>
+      <c r="B109" s="19" t="n"/>
+      <c r="C109" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Dây thép buộc 1 ly</t>
+        </is>
+      </c>
+      <c r="D109" s="19" t="n"/>
+      <c r="E109" s="19" t="n"/>
+      <c r="F109" s="30" t="inlineStr">
+        <is>
+          <t>Dây thép buộc 1 ly</t>
+        </is>
+      </c>
+      <c r="G109" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H109" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="I109" s="42">
+        <f>D105*H109</f>
+        <v/>
+      </c>
+      <c r="J109" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="B110" s="52" t="inlineStr">
+        <is>
+          <t>AC.31111</t>
+        </is>
+      </c>
+      <c r="C110" s="53" t="inlineStr">
+        <is>
+          <t>Khe co giãn răng lược thép D=100mm</t>
+        </is>
+      </c>
+      <c r="D110" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J83</f>
+        <v/>
+      </c>
+      <c r="E110" s="52" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F110" s="55" t="n"/>
+      <c r="G110" s="55" t="n"/>
+      <c r="H110" s="55" t="n"/>
+      <c r="I110" s="55" t="n"/>
+      <c r="J110" s="55" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="19" t="n"/>
+      <c r="B111" s="19" t="n"/>
+      <c r="C111" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép tấm răng lược hợp kim mạ kẽm D=100mm</t>
+        </is>
+      </c>
+      <c r="D111" s="19" t="n"/>
+      <c r="E111" s="19" t="n"/>
+      <c r="F111" s="30" t="inlineStr">
+        <is>
+          <t>Thép tấm răng lược hợp kim mạ kẽm D=100mm</t>
+        </is>
+      </c>
+      <c r="G111" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H111" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="42">
+        <f>D110*H111</f>
+        <v/>
+      </c>
+      <c r="J111" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="19" t="n"/>
+      <c r="B112" s="19" t="n"/>
+      <c r="C112" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Máng thoát nước cao su đàn hồi</t>
+        </is>
+      </c>
+      <c r="D112" s="19" t="n"/>
+      <c r="E112" s="19" t="n"/>
+      <c r="F112" s="30" t="inlineStr">
+        <is>
+          <t>Máng thoát nước cao su đàn hồi</t>
+        </is>
+      </c>
+      <c r="G112" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H112" s="42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I112" s="42">
+        <f>D110*H112</f>
+        <v/>
+      </c>
+      <c r="J112" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="19" t="n"/>
+      <c r="B113" s="19" t="n"/>
+      <c r="C113" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Bu-lông neo M24 cường độ cao</t>
+        </is>
+      </c>
+      <c r="D113" s="19" t="n"/>
+      <c r="E113" s="19" t="n"/>
+      <c r="F113" s="30" t="inlineStr">
+        <is>
+          <t>Bu-lông neo M24 cường độ cao</t>
+        </is>
+      </c>
+      <c r="G113" s="31" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="H113" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I113" s="42">
+        <f>D110*H113</f>
+        <v/>
+      </c>
+      <c r="J113" s="30" t="inlineStr">
+        <is>
+          <t>ASTM A325</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="52" t="n">
+        <v>21</v>
+      </c>
+      <c r="B114" s="52" t="inlineStr">
+        <is>
+          <t>AF.41111</t>
+        </is>
+      </c>
+      <c r="C114" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông bản quá độ sau mố M1, M2 mác C30</t>
+        </is>
+      </c>
+      <c r="D114" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J86</f>
+        <v/>
+      </c>
+      <c r="E114" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F114" s="55" t="n"/>
+      <c r="G114" s="55" t="n"/>
+      <c r="H114" s="55" t="n"/>
+      <c r="I114" s="55" t="n"/>
+      <c r="J114" s="55" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="19" t="n"/>
+      <c r="B115" s="19" t="n"/>
+      <c r="C115" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 bản quá độ</t>
+        </is>
+      </c>
+      <c r="D115" s="19" t="n"/>
+      <c r="E115" s="19" t="n"/>
+      <c r="F115" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 bản quá độ</t>
+        </is>
+      </c>
+      <c r="G115" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H115" s="42" t="n">
+        <v>385</v>
+      </c>
+      <c r="I115" s="42">
+        <f>D114*H115</f>
+        <v/>
+      </c>
+      <c r="J115" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="19" t="n"/>
+      <c r="B116" s="19" t="n"/>
+      <c r="C116" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="D116" s="19" t="n"/>
+      <c r="E116" s="19" t="n"/>
+      <c r="F116" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa Mk&gt;=2.0</t>
+        </is>
+      </c>
+      <c r="G116" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H116" s="56" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I116" s="42">
+        <f>D114*H116</f>
+        <v/>
+      </c>
+      <c r="J116" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="19" t="n"/>
+      <c r="B117" s="19" t="n"/>
+      <c r="C117" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="D117" s="19" t="n"/>
+      <c r="E117" s="19" t="n"/>
+      <c r="F117" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch</t>
+        </is>
+      </c>
+      <c r="G117" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H117" s="56" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I117" s="42">
+        <f>D114*H117</f>
+        <v/>
+      </c>
+      <c r="J117" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="19" t="n"/>
+      <c r="B118" s="19" t="n"/>
+      <c r="C118" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="D118" s="19" t="n"/>
+      <c r="E118" s="19" t="n"/>
+      <c r="F118" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch trộn bê tông</t>
+        </is>
+      </c>
+      <c r="G118" s="31" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="H118" s="42" t="n">
+        <v>180</v>
+      </c>
+      <c r="I118" s="42">
+        <f>D114*H118</f>
+        <v/>
+      </c>
+      <c r="J118" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="19" t="n"/>
+      <c r="B119" s="19" t="n"/>
+      <c r="C119" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép bản quá độ dọc vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="D119" s="19" t="n"/>
+      <c r="E119" s="19" t="n"/>
+      <c r="F119" s="30" t="inlineStr">
+        <is>
+          <t>Thép bản quá độ dọc vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="G119" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H119" s="42" t="n">
+        <v>110</v>
+      </c>
+      <c r="I119" s="42">
+        <f>D114*H119</f>
+        <v/>
+      </c>
+      <c r="J119" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="19" t="n"/>
+      <c r="B120" s="19" t="n"/>
+      <c r="C120" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép bản quá độ phân bố vằn Ø12 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="D120" s="19" t="n"/>
+      <c r="E120" s="19" t="n"/>
+      <c r="F120" s="30" t="inlineStr">
+        <is>
+          <t>Thép bản quá độ phân bố vằn Ø12 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="G120" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H120" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="I120" s="42">
+        <f>D114*H120</f>
+        <v/>
+      </c>
+      <c r="J120" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="52" t="n">
+        <v>22</v>
+      </c>
+      <c r="B121" s="52" t="inlineStr">
+        <is>
+          <t>AB.21111</t>
+        </is>
+      </c>
+      <c r="C121" s="53" t="inlineStr">
+        <is>
+          <t>Đắp vật liệu dạng hạt chọn lọc sau mố K98</t>
+        </is>
+      </c>
+      <c r="D121" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J89</f>
+        <v/>
+      </c>
+      <c r="E121" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F121" s="55" t="n"/>
+      <c r="G121" s="55" t="n"/>
+      <c r="H121" s="55" t="n"/>
+      <c r="I121" s="55" t="n"/>
+      <c r="J121" s="55" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="19" t="n"/>
+      <c r="B122" s="19" t="n"/>
+      <c r="C122" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đất đắp nền đường sau mố K98</t>
+        </is>
+      </c>
+      <c r="D122" s="19" t="n"/>
+      <c r="E122" s="19" t="n"/>
+      <c r="F122" s="30" t="inlineStr">
+        <is>
+          <t>Đất đắp nền đường sau mố K98</t>
+        </is>
+      </c>
+      <c r="G122" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H122" s="42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I122" s="42">
+        <f>D121*H122</f>
+        <v/>
+      </c>
+      <c r="J122" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 9436:2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="19" t="n"/>
+      <c r="B123" s="19" t="n"/>
+      <c r="C123" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Vải địa kỹ thuật không dệt lọc ngược</t>
+        </is>
+      </c>
+      <c r="D123" s="19" t="n"/>
+      <c r="E123" s="19" t="n"/>
+      <c r="F123" s="30" t="inlineStr">
+        <is>
+          <t>Vải địa kỹ thuật không dệt lọc ngược</t>
+        </is>
+      </c>
+      <c r="G123" s="31" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H123" s="56" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I123" s="42">
+        <f>D121*H123</f>
+        <v/>
+      </c>
+      <c r="J123" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 9865:2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="52" t="n">
+        <v>23</v>
+      </c>
+      <c r="B124" s="52" t="inlineStr">
+        <is>
+          <t>AF.42111</t>
+        </is>
+      </c>
+      <c r="C124" s="53" t="inlineStr">
+        <is>
+          <t>Bê tông gờ lan can mác C25 và lắp tay vịn thép</t>
+        </is>
+      </c>
+      <c r="D124" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J91</f>
+        <v/>
+      </c>
+      <c r="E124" s="52" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F124" s="55" t="n"/>
+      <c r="G124" s="55" t="n"/>
+      <c r="H124" s="55" t="n"/>
+      <c r="I124" s="55" t="n"/>
+      <c r="J124" s="55" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="19" t="n"/>
+      <c r="B125" s="19" t="n"/>
+      <c r="C125" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 gờ lan can</t>
+        </is>
+      </c>
+      <c r="D125" s="19" t="n"/>
+      <c r="E125" s="19" t="n"/>
+      <c r="F125" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 gờ lan can</t>
+        </is>
+      </c>
+      <c r="G125" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H125" s="42" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="I125" s="42">
+        <f>D124*H125</f>
+        <v/>
+      </c>
+      <c r="J125" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="19" t="n"/>
+      <c r="B126" s="19" t="n"/>
+      <c r="C126" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng</t>
+        </is>
+      </c>
+      <c r="D126" s="19" t="n"/>
+      <c r="E126" s="19" t="n"/>
+      <c r="F126" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng</t>
+        </is>
+      </c>
+      <c r="G126" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H126" s="56" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I126" s="42">
+        <f>D124*H126</f>
+        <v/>
+      </c>
+      <c r="J126" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="19" t="n"/>
+      <c r="B127" s="19" t="n"/>
+      <c r="C127" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá dăm 1x2</t>
+        </is>
+      </c>
+      <c r="D127" s="19" t="n"/>
+      <c r="E127" s="19" t="n"/>
+      <c r="F127" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2</t>
+        </is>
+      </c>
+      <c r="G127" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H127" s="56" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="I127" s="42">
+        <f>D124*H127</f>
+        <v/>
+      </c>
+      <c r="J127" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="19" t="n"/>
+      <c r="B128" s="19" t="n"/>
+      <c r="C128" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Thép cốt gờ lan can vằn Ø12 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="D128" s="19" t="n"/>
+      <c r="E128" s="19" t="n"/>
+      <c r="F128" s="30" t="inlineStr">
+        <is>
+          <t>Thép cốt gờ lan can vằn Ø12 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="G128" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H128" s="42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I128" s="42">
+        <f>D124*H128</f>
+        <v/>
+      </c>
+      <c r="J128" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="19" t="n"/>
+      <c r="B129" s="19" t="n"/>
+      <c r="C129" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Tay vịn lan can thép mạ kẽm nhúng nóng Ø114</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="n"/>
+      <c r="E129" s="19" t="n"/>
+      <c r="F129" s="30" t="inlineStr">
+        <is>
+          <t>Tay vịn lan can thép mạ kẽm nhúng nóng Ø114</t>
+        </is>
+      </c>
+      <c r="G129" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H129" s="42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I129" s="42">
+        <f>D124*H129</f>
+        <v/>
+      </c>
+      <c r="J129" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="52" t="n">
+        <v>24</v>
+      </c>
+      <c r="B130" s="52" t="inlineStr">
+        <is>
+          <t>AC.41111</t>
+        </is>
+      </c>
+      <c r="C130" s="53" t="inlineStr">
+        <is>
+          <t>Hệ thống thoát nước mặt cầu (24 cụm hố thu &amp; ống dẫn)</t>
+        </is>
+      </c>
+      <c r="D130" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J93</f>
+        <v/>
+      </c>
+      <c r="E130" s="52" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="F130" s="55" t="n"/>
+      <c r="G130" s="55" t="n"/>
+      <c r="H130" s="55" t="n"/>
+      <c r="I130" s="55" t="n"/>
+      <c r="J130" s="55" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="19" t="n"/>
+      <c r="B131" s="19" t="n"/>
+      <c r="C131" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Phễu gang thu nước mặt cầu có lưới chắn</t>
+        </is>
+      </c>
+      <c r="D131" s="19" t="n"/>
+      <c r="E131" s="19" t="n"/>
+      <c r="F131" s="30" t="inlineStr">
+        <is>
+          <t>Phễu gang thu nước mặt cầu có lưới chắn</t>
+        </is>
+      </c>
+      <c r="G131" s="31" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="H131" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="42">
+        <f>D130*H131</f>
+        <v/>
+      </c>
+      <c r="J131" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="19" t="n"/>
+      <c r="B132" s="19" t="n"/>
+      <c r="C132" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Ống thoát nước nhựa uPVC Ø110 dày 3.2mm</t>
+        </is>
+      </c>
+      <c r="D132" s="19" t="n"/>
+      <c r="E132" s="19" t="n"/>
+      <c r="F132" s="30" t="inlineStr">
+        <is>
+          <t>Ống thoát nước nhựa uPVC Ø110 dày 3.2mm</t>
+        </is>
+      </c>
+      <c r="G132" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H132" s="42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I132" s="42">
+        <f>D130*H132</f>
+        <v/>
+      </c>
+      <c r="J132" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 8491:2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="52" t="n">
+        <v>25</v>
+      </c>
+      <c r="B133" s="52" t="inlineStr">
+        <is>
+          <t>AD.11111</t>
+        </is>
+      </c>
+      <c r="C133" s="53" t="inlineStr">
+        <is>
+          <t>Lớp phun chống thấm &amp; thảm bê tông nhựa chặt C12.5 dày 7cm</t>
+        </is>
+      </c>
+      <c r="D133" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J95</f>
+        <v/>
+      </c>
+      <c r="E133" s="52" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F133" s="55" t="n"/>
+      <c r="G133" s="55" t="n"/>
+      <c r="H133" s="55" t="n"/>
+      <c r="I133" s="55" t="n"/>
+      <c r="J133" s="55" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="19" t="n"/>
+      <c r="B134" s="19" t="n"/>
+      <c r="C134" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Màng chống thấm mặt cầu Polymer cải tiến</t>
+        </is>
+      </c>
+      <c r="D134" s="19" t="n"/>
+      <c r="E134" s="19" t="n"/>
+      <c r="F134" s="30" t="inlineStr">
+        <is>
+          <t>Màng chống thấm mặt cầu Polymer cải tiến</t>
+        </is>
+      </c>
+      <c r="G134" s="31" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H134" s="42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I134" s="42">
+        <f>D133*H134</f>
+        <v/>
+      </c>
+      <c r="J134" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="19" t="n"/>
+      <c r="B135" s="19" t="n"/>
+      <c r="C135" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Bê tông nhựa chặt C12.5 rải nóng</t>
+        </is>
+      </c>
+      <c r="D135" s="19" t="n"/>
+      <c r="E135" s="19" t="n"/>
+      <c r="F135" s="30" t="inlineStr">
+        <is>
+          <t>Bê tông nhựa chặt C12.5 rải nóng</t>
+        </is>
+      </c>
+      <c r="G135" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="H135" s="56" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="I135" s="42">
+        <f>D133*H135</f>
+        <v/>
+      </c>
+      <c r="J135" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 8819:2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="19" t="n"/>
+      <c r="B136" s="19" t="n"/>
+      <c r="C136" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Nhựa dính bám Tack coat</t>
+        </is>
+      </c>
+      <c r="D136" s="19" t="n"/>
+      <c r="E136" s="19" t="n"/>
+      <c r="F136" s="30" t="inlineStr">
+        <is>
+          <t>Nhựa dính bám Tack coat</t>
+        </is>
+      </c>
+      <c r="G136" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H136" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I136" s="42">
+        <f>D133*H136</f>
+        <v/>
+      </c>
+      <c r="J136" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 8819:2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="52" t="n">
+        <v>26</v>
+      </c>
+      <c r="B137" s="52" t="inlineStr">
+        <is>
+          <t>AL.11111</t>
+        </is>
+      </c>
+      <c r="C137" s="53" t="inlineStr">
+        <is>
+          <t>Gia cố mái taluy tứ nón mố bằng đá hộc xây VXM M100</t>
+        </is>
+      </c>
+      <c r="D137" s="54">
+        <f>QS_DIEN_GIAI_CHI_TIET!J97</f>
+        <v/>
+      </c>
+      <c r="E137" s="52" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F137" s="55" t="n"/>
+      <c r="G137" s="55" t="n"/>
+      <c r="H137" s="55" t="n"/>
+      <c r="I137" s="55" t="n"/>
+      <c r="J137" s="55" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="19" t="n"/>
+      <c r="B138" s="19" t="n"/>
+      <c r="C138" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Đá hộc 20x30cm kè tứ nón</t>
+        </is>
+      </c>
+      <c r="D138" s="19" t="n"/>
+      <c r="E138" s="19" t="n"/>
+      <c r="F138" s="30" t="inlineStr">
+        <is>
+          <t>Đá hộc 20x30cm kè tứ nón</t>
+        </is>
+      </c>
+      <c r="G138" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H138" s="42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I138" s="42">
+        <f>D137*H138</f>
+        <v/>
+      </c>
+      <c r="J138" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="19" t="n"/>
+      <c r="B139" s="19" t="n"/>
+      <c r="C139" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Xi măng PCB40 vữa xây M100</t>
+        </is>
+      </c>
+      <c r="D139" s="19" t="n"/>
+      <c r="E139" s="19" t="n"/>
+      <c r="F139" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 vữa xây M100</t>
+        </is>
+      </c>
+      <c r="G139" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H139" s="42" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="I139" s="42">
+        <f>D137*H139</f>
+        <v/>
+      </c>
+      <c r="J139" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="19" t="n"/>
+      <c r="B140" s="19" t="n"/>
+      <c r="C140" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Cát vàng vữa xây M100</t>
+        </is>
+      </c>
+      <c r="D140" s="19" t="n"/>
+      <c r="E140" s="19" t="n"/>
+      <c r="F140" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng vữa xây M100</t>
+        </is>
+      </c>
+      <c r="G140" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="H140" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I140" s="42">
+        <f>D137*H140</f>
+        <v/>
+      </c>
+      <c r="J140" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:K43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>DỰ ÁN: CAO TỐC TUYÊN QUANG - HÀ GIANG (GIAI ĐOẠN 1) - CẦU KM19+529.080</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>BẢNG TỔNG HỢP NHU CẦU VẬT TƯ TOÀN CÔNG TRÌNH &amp; KẾ HOẠCH CUNG ỨNG (BOM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tổng hợp tự động 100% công thức (=SUMIF) từ bảng phân rã WBS; Kế hoạch phân bổ theo 4 giai đoạn thi công</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Tên chủng loại vật tư</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Tiêu chuẩn kỹ thuật</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ĐVT</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Hao phí định mức lý thuyết</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hao hụt TT12 (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Tổng nhu cầu cung ứng (BOM)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>GĐ 1: Cọc nhồi</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>GĐ 2: Mố &amp; Trụ</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>GĐ 3: Dầm &amp; Mặt cầu</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>GĐ 4: Hoàn thiện</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="57" t="n"/>
+      <c r="B6" s="58" t="inlineStr">
+        <is>
+          <t>I. SẮT THÉP CÁC LOẠI (CỐT THÉP, CÁP DỰ ỨNG LỰC &amp; PHỤ KIỆN)</t>
+        </is>
+      </c>
+      <c r="C6" s="57" t="n"/>
+      <c r="D6" s="57" t="n"/>
+      <c r="E6" s="57" t="n"/>
+      <c r="F6" s="57" t="n"/>
+      <c r="G6" s="57" t="n"/>
+      <c r="H6" s="57" t="n"/>
+      <c r="I6" s="57" t="n"/>
+      <c r="J6" s="57" t="n"/>
+      <c r="K6" s="57" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Thép đai tròn trơn Ø10 (CB240-T)</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E7" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ø10*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F7" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G7" s="60">
+        <f>E7*(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="42">
+        <f>G7*0.4</f>
+        <v/>
+      </c>
+      <c r="I7" s="42">
+        <f>G7*0.2</f>
+        <v/>
+      </c>
+      <c r="J7" s="42">
+        <f>G7*0.4</f>
+        <v/>
+      </c>
+      <c r="K7" s="42">
+        <f>G7*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Thép cốt vằn Ø12 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E8" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ø12*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)/1000</f>
+        <v/>
+      </c>
+      <c r="F8" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G8" s="60">
+        <f>E8*(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="42">
+        <f>G8*0.0</f>
+        <v/>
+      </c>
+      <c r="I8" s="42">
+        <f>G8*0.0</f>
+        <v/>
+      </c>
+      <c r="J8" s="42">
+        <f>G8*0.0</f>
+        <v/>
+      </c>
+      <c r="K8" s="42">
+        <f>G8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Thép bản cánh &amp; mặt cầu vằn Ø14 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E9" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ø14*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F9" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G9" s="60">
+        <f>E9*(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="42">
+        <f>G9*0.0</f>
+        <v/>
+      </c>
+      <c r="I9" s="42">
+        <f>G9*0.0</f>
+        <v/>
+      </c>
+      <c r="J9" s="42">
+        <f>G9*1.0</f>
+        <v/>
+      </c>
+      <c r="K9" s="42">
+        <f>G9*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>Thép đai &amp; sườn dầm vằn Ø16 (CB400-V)</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E10" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ø16*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F10" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G10" s="60">
+        <f>E10*(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="42">
+        <f>G10*0.25</f>
+        <v/>
+      </c>
+      <c r="I10" s="42">
+        <f>G10*0.15</f>
+        <v/>
+      </c>
+      <c r="J10" s="42">
+        <f>G10*0.5</f>
+        <v/>
+      </c>
+      <c r="K10" s="42">
+        <f>G10*0.1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>Thép phân bố bệ móng vằn Ø20 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E11" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ø20*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F11" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G11" s="60">
+        <f>E11*(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="42">
+        <f>G11*0.0</f>
+        <v/>
+      </c>
+      <c r="I11" s="42">
+        <f>G11*1.0</f>
+        <v/>
+      </c>
+      <c r="J11" s="42">
+        <f>G11*0.0</f>
+        <v/>
+      </c>
+      <c r="K11" s="42">
+        <f>G11*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>Thép chủ cọc khoan nhồi vằn Ø25 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E12" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ø25*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F12" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G12" s="60">
+        <f>E12*(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="42">
+        <f>G12*1.0</f>
+        <v/>
+      </c>
+      <c r="I12" s="42">
+        <f>G12*0.0</f>
+        <v/>
+      </c>
+      <c r="J12" s="42">
+        <f>G12*0.0</f>
+        <v/>
+      </c>
+      <c r="K12" s="42">
+        <f>G12*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>Thép thân mố &amp; xà mũ vằn Ø28 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E13" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ø28*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G13" s="60">
+        <f>E13*(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="42">
+        <f>G13*0.0</f>
+        <v/>
+      </c>
+      <c r="I13" s="42">
+        <f>G13*1.0</f>
+        <v/>
+      </c>
+      <c r="J13" s="42">
+        <f>G13*0.0</f>
+        <v/>
+      </c>
+      <c r="K13" s="42">
+        <f>G13*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Thép bệ móng &amp; thân trụ vằn Ø32 (CB500-V)</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E14" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ø32*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F14" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G14" s="60">
+        <f>E14*(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="42">
+        <f>G14*0.0</f>
+        <v/>
+      </c>
+      <c r="I14" s="42">
+        <f>G14*1.0</f>
+        <v/>
+      </c>
+      <c r="J14" s="42">
+        <f>G14*0.0</f>
+        <v/>
+      </c>
+      <c r="K14" s="42">
+        <f>G14*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>Cáp dự ứng lực tao 15.2mm Grade 270</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>ASTM A416 Gr270</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E15" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Cáp dự ứng lực*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F15" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G15" s="60">
+        <f>E15*(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="42">
+        <f>G15*0.0</f>
+        <v/>
+      </c>
+      <c r="I15" s="42">
+        <f>G15*0.0</f>
+        <v/>
+      </c>
+      <c r="J15" s="42">
+        <f>G15*1.0</f>
+        <v/>
+      </c>
+      <c r="K15" s="42">
+        <f>G15*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>Bộ neo chùm dự ứng lực công tác</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="E16" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Bộ neo chùm*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F16" s="59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G16" s="60">
+        <f>E16*(1+F16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="42">
+        <f>G16*0.0</f>
+        <v/>
+      </c>
+      <c r="I16" s="42">
+        <f>G16*0.0</f>
+        <v/>
+      </c>
+      <c r="J16" s="42">
+        <f>G16*1.0</f>
+        <v/>
+      </c>
+      <c r="K16" s="42">
+        <f>G16*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Ống ghen tôn mạ kẽm luồn cáp DƯL</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E17" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ống ghen tôn*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F17" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G17" s="60">
+        <f>E17*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="42">
+        <f>G17*0.0</f>
+        <v/>
+      </c>
+      <c r="I17" s="42">
+        <f>G17*0.0</f>
+        <v/>
+      </c>
+      <c r="J17" s="42">
+        <f>G17*1.0</f>
+        <v/>
+      </c>
+      <c r="K17" s="42">
+        <f>G17*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Ống siêu âm cọc nhồi thép Ø60x2</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>ASTM A53 / TCVN 9395</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E18" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ống siêu âm*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F18" s="59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G18" s="60">
+        <f>E18*(1+F18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="42">
+        <f>G18*1.0</f>
+        <v/>
+      </c>
+      <c r="I18" s="42">
+        <f>G18*0.0</f>
+        <v/>
+      </c>
+      <c r="J18" s="42">
+        <f>G18*0.0</f>
+        <v/>
+      </c>
+      <c r="K18" s="42">
+        <f>G18*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Ống vách thép dẫn hướng D1300 d=8mm</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 9395:2012</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E19" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Ống vách thép*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F19" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G19" s="60">
+        <f>E19*(1+F19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="42">
+        <f>G19*1.0</f>
+        <v/>
+      </c>
+      <c r="I19" s="42">
+        <f>G19*0.0</f>
+        <v/>
+      </c>
+      <c r="J19" s="42">
+        <f>G19*0.0</f>
+        <v/>
+      </c>
+      <c r="K19" s="42">
+        <f>G19*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Tay vịn lan can thép mạ kẽm nhúng nóng Ø114</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E20" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Tay vịn*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F20" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G20" s="60">
+        <f>E20*(1+F20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="42">
+        <f>G20*0.0</f>
+        <v/>
+      </c>
+      <c r="I20" s="42">
+        <f>G20*0.0</f>
+        <v/>
+      </c>
+      <c r="J20" s="42">
+        <f>G20*0.0</f>
+        <v/>
+      </c>
+      <c r="K20" s="42">
+        <f>G20*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Thép tấm khe co giãn răng lược D=100mm</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E21" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Thép tấm răng lược*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F21" s="59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G21" s="60">
+        <f>E21*(1+F21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="42">
+        <f>G21*0.0</f>
+        <v/>
+      </c>
+      <c r="I21" s="42">
+        <f>G21*0.0</f>
+        <v/>
+      </c>
+      <c r="J21" s="42">
+        <f>G21*0.0</f>
+        <v/>
+      </c>
+      <c r="K21" s="42">
+        <f>G21*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Dây thép buộc 1 ly</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 1651:2018</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E22" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Dây thép buộc*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F22" s="59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G22" s="60">
+        <f>E22*(1+F22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="42">
+        <f>G22*0.35</f>
+        <v/>
+      </c>
+      <c r="I22" s="42">
+        <f>G22*0.25</f>
+        <v/>
+      </c>
+      <c r="J22" s="42">
+        <f>G22*0.35</f>
+        <v/>
+      </c>
+      <c r="K22" s="42">
+        <f>G22*0.05</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Que hàn điện E42/E50</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 3223:2000</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E23" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Que hàn điện*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F23" s="59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G23" s="60">
+        <f>E23*(1+F23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="42">
+        <f>G23*0.5</f>
+        <v/>
+      </c>
+      <c r="I23" s="42">
+        <f>G23*0.3</f>
+        <v/>
+      </c>
+      <c r="J23" s="42">
+        <f>G23*0.2</f>
+        <v/>
+      </c>
+      <c r="K23" s="42">
+        <f>G23*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="57" t="n"/>
+      <c r="B24" s="58" t="inlineStr">
+        <is>
+          <t>II. KHOÁNG XÂY DỰNG &amp; CẤP PHỐI BÊ TÔNG</t>
+        </is>
+      </c>
+      <c r="C24" s="57" t="n"/>
+      <c r="D24" s="57" t="n"/>
+      <c r="E24" s="57" t="n"/>
+      <c r="F24" s="57" t="n"/>
+      <c r="G24" s="57" t="n"/>
+      <c r="H24" s="57" t="n"/>
+      <c r="I24" s="57" t="n"/>
+      <c r="J24" s="57" t="n"/>
+      <c r="K24" s="57" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Xi măng PCB40 (quy đổi Tấn)</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 6260:2020</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E25" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Xi măng PCB40*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)/1000</f>
+        <v/>
+      </c>
+      <c r="F25" s="59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G25" s="60">
+        <f>E25*(1+F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="42">
+        <f>G25*0.25</f>
+        <v/>
+      </c>
+      <c r="I25" s="42">
+        <f>G25*0.3</f>
+        <v/>
+      </c>
+      <c r="J25" s="42">
+        <f>G25*0.4</f>
+        <v/>
+      </c>
+      <c r="K25" s="42">
+        <f>G25*0.05</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cát vàng sàng rửa đúc bê tông (Mk &gt;= 2.0)</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E26" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Cát vàng*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F26" s="59" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G26" s="60">
+        <f>E26*(1+F26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="42">
+        <f>G26*0.25</f>
+        <v/>
+      </c>
+      <c r="I26" s="42">
+        <f>G26*0.3</f>
+        <v/>
+      </c>
+      <c r="J26" s="42">
+        <f>G26*0.4</f>
+        <v/>
+      </c>
+      <c r="K26" s="42">
+        <f>G26*0.05</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Đá dăm 1x2 sạch chọn lọc</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 7570:2006</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E27" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Đá dăm 1x2*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F27" s="59" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G27" s="60">
+        <f>E27*(1+F27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="42">
+        <f>G27*0.25</f>
+        <v/>
+      </c>
+      <c r="I27" s="42">
+        <f>G27*0.3</f>
+        <v/>
+      </c>
+      <c r="J27" s="42">
+        <f>G27*0.4</f>
+        <v/>
+      </c>
+      <c r="K27" s="42">
+        <f>G27*0.05</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Đá hộc 20x30cm kè tứ nón mố</t>
+        </is>
+      </c>
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E28" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Đá hộc*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F28" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G28" s="60">
+        <f>E28*(1+F28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="42">
+        <f>G28*0.0</f>
+        <v/>
+      </c>
+      <c r="I28" s="42">
+        <f>G28*0.0</f>
+        <v/>
+      </c>
+      <c r="J28" s="42">
+        <f>G28*0.0</f>
+        <v/>
+      </c>
+      <c r="K28" s="42">
+        <f>G28*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Đất đắp nền đường sau mố K98</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 9436:2012</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E29" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Đất đắp*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F29" s="59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G29" s="60">
+        <f>E29*(1+F29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="42">
+        <f>G29*0.0</f>
+        <v/>
+      </c>
+      <c r="I29" s="42">
+        <f>G29*0.0</f>
+        <v/>
+      </c>
+      <c r="J29" s="42">
+        <f>G29*0.0</f>
+        <v/>
+      </c>
+      <c r="K29" s="42">
+        <f>G29*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Nước sạch thi công &amp; dưỡng hộ (quy đổi m3)</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 4506:2012</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E30" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Nước sạch*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)/1000</f>
+        <v/>
+      </c>
+      <c r="F30" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G30" s="60">
+        <f>E30*(1+F30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="42">
+        <f>G30*0.25</f>
+        <v/>
+      </c>
+      <c r="I30" s="42">
+        <f>G30*0.3</f>
+        <v/>
+      </c>
+      <c r="J30" s="42">
+        <f>G30*0.4</f>
+        <v/>
+      </c>
+      <c r="K30" s="42">
+        <f>G30*0.05</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="57" t="n"/>
+      <c r="B31" s="58" t="inlineStr">
+        <is>
+          <t>III. PHỤ GIA VÀ HÓA CHẤT XÂY DỰNG</t>
+        </is>
+      </c>
+      <c r="C31" s="57" t="n"/>
+      <c r="D31" s="57" t="n"/>
+      <c r="E31" s="57" t="n"/>
+      <c r="F31" s="57" t="n"/>
+      <c r="G31" s="57" t="n"/>
+      <c r="H31" s="57" t="n"/>
+      <c r="I31" s="57" t="n"/>
+      <c r="J31" s="57" t="n"/>
+      <c r="K31" s="57" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia siêu dẻo Polycarboxylate thế hệ 3</t>
+        </is>
+      </c>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type F/G</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E32" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Phụ gia siêu dẻo*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F32" s="59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G32" s="60">
+        <f>E32*(1+F32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="42">
+        <f>G32*0.0</f>
+        <v/>
+      </c>
+      <c r="I32" s="42">
+        <f>G32*0.3</f>
+        <v/>
+      </c>
+      <c r="J32" s="42">
+        <f>G32*0.7</f>
+        <v/>
+      </c>
+      <c r="K32" s="42">
+        <f>G32*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Phụ gia hoá dẻo chậm đông kết</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C494 Type G</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E33" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Phụ gia hoá dẻo*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F33" s="59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G33" s="60">
+        <f>E33*(1+F33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="42">
+        <f>G33*1.0</f>
+        <v/>
+      </c>
+      <c r="I33" s="42">
+        <f>G33*0.0</f>
+        <v/>
+      </c>
+      <c r="J33" s="42">
+        <f>G33*0.0</f>
+        <v/>
+      </c>
+      <c r="K33" s="42">
+        <f>G33*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Vữa rót không co ngót bơm ghen SikaGrout 214-11</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>ASTM C1107</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E34" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Vữa không co ngót*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F34" s="59" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G34" s="60">
+        <f>E34*(1+F34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="42">
+        <f>G34*0.0</f>
+        <v/>
+      </c>
+      <c r="I34" s="42">
+        <f>G34*0.0</f>
+        <v/>
+      </c>
+      <c r="J34" s="42">
+        <f>G34*1.0</f>
+        <v/>
+      </c>
+      <c r="K34" s="42">
+        <f>G34*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Bột sét Bentonite tạo vách cọc khoan nhồi</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 9395:2012</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E35" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Bentonite*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)/1000</f>
+        <v/>
+      </c>
+      <c r="F35" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G35" s="60">
+        <f>E35*(1+F35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="42">
+        <f>G35*1.0</f>
+        <v/>
+      </c>
+      <c r="I35" s="42">
+        <f>G35*0.0</f>
+        <v/>
+      </c>
+      <c r="J35" s="42">
+        <f>G35*0.0</f>
+        <v/>
+      </c>
+      <c r="K35" s="42">
+        <f>G35*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="57" t="n"/>
+      <c r="B36" s="58" t="inlineStr">
+        <is>
+          <t>IV. PHỤ KIỆN &amp; VẬT LIỆU HOÀN THIỆN CẦU</t>
+        </is>
+      </c>
+      <c r="C36" s="57" t="n"/>
+      <c r="D36" s="57" t="n"/>
+      <c r="E36" s="57" t="n"/>
+      <c r="F36" s="57" t="n"/>
+      <c r="G36" s="57" t="n"/>
+      <c r="H36" s="57" t="n"/>
+      <c r="I36" s="57" t="n"/>
+      <c r="J36" s="57" t="n"/>
+      <c r="K36" s="57" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>Gối chậu cao su cốt bản thép chịu lực</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="E37" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Gối chậu*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F37" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="60">
+        <f>E37*(1+F37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="42">
+        <f>G37*0.0</f>
+        <v/>
+      </c>
+      <c r="I37" s="42">
+        <f>G37*0.0</f>
+        <v/>
+      </c>
+      <c r="J37" s="42">
+        <f>G37*1.0</f>
+        <v/>
+      </c>
+      <c r="K37" s="42">
+        <f>G37*0.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>Màng / Sơn chống thấm mặt cầu Polymer cải tiến</t>
+        </is>
+      </c>
+      <c r="C38" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="E38" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Màng chống thấm*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F38" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G38" s="60">
+        <f>E38*(1+F38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="42">
+        <f>G38*0.0</f>
+        <v/>
+      </c>
+      <c r="I38" s="42">
+        <f>G38*0.0</f>
+        <v/>
+      </c>
+      <c r="J38" s="42">
+        <f>G38*0.0</f>
+        <v/>
+      </c>
+      <c r="K38" s="42">
+        <f>G38*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>Bê tông nhựa chặt C12.5 rải nóng</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 8819:2011</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>Tấn</t>
+        </is>
+      </c>
+      <c r="E39" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Bê tông nhựa*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F39" s="59" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G39" s="60">
+        <f>E39*(1+F39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="42">
+        <f>G39*0.0</f>
+        <v/>
+      </c>
+      <c r="I39" s="42">
+        <f>G39*0.0</f>
+        <v/>
+      </c>
+      <c r="J39" s="42">
+        <f>G39*0.0</f>
+        <v/>
+      </c>
+      <c r="K39" s="42">
+        <f>G39*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>Vải địa kỹ thuật không dệt lọc ngược</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 9865:2013</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="E40" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Vải địa*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F40" s="59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G40" s="60">
+        <f>E40*(1+F40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="42">
+        <f>G40*0.0</f>
+        <v/>
+      </c>
+      <c r="I40" s="42">
+        <f>G40*0.0</f>
+        <v/>
+      </c>
+      <c r="J40" s="42">
+        <f>G40*0.0</f>
+        <v/>
+      </c>
+      <c r="K40" s="42">
+        <f>G40*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>Phễu gang thu nước mặt cầu có lưới chắn</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 11823:2017</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="E41" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Phễu gang*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F41" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="60">
+        <f>E41*(1+F41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="42">
+        <f>G41*0.0</f>
+        <v/>
+      </c>
+      <c r="I41" s="42">
+        <f>G41*0.0</f>
+        <v/>
+      </c>
+      <c r="J41" s="42">
+        <f>G41*0.0</f>
+        <v/>
+      </c>
+      <c r="K41" s="42">
+        <f>G41*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>Ống thoát nước nhựa uPVC Ø110 dày 3.2mm</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 8491:2011</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E42" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*uPVC Ø110*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F42" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G42" s="60">
+        <f>E42*(1+F42)</f>
+        <v/>
+      </c>
+      <c r="H42" s="42">
+        <f>G42*0.0</f>
+        <v/>
+      </c>
+      <c r="I42" s="42">
+        <f>G42*0.0</f>
+        <v/>
+      </c>
+      <c r="J42" s="42">
+        <f>G42*0.0</f>
+        <v/>
+      </c>
+      <c r="K42" s="42">
+        <f>G42*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>Nhựa dính bám Tack coat</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="inlineStr">
+        <is>
+          <t>TCVN 8819:2011</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E43" s="42">
+        <f>SUMIF(PHAN_TICH_VAT_TU_WBS!$F$6:$F$140, "*Nhựa dính bám*", PHAN_TICH_VAT_TU_WBS!$I$6:$I$140)</f>
+        <v/>
+      </c>
+      <c r="F43" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G43" s="60">
+        <f>E43*(1+F43)</f>
+        <v/>
+      </c>
+      <c r="H43" s="42">
+        <f>G43*0.0</f>
+        <v/>
+      </c>
+      <c r="I43" s="42">
+        <f>G43*0.0</f>
+        <v/>
+      </c>
+      <c r="J43" s="42">
+        <f>G43*0.0</f>
+        <v/>
+      </c>
+      <c r="K43" s="42">
+        <f>G43*1.0</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
+++ b/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
@@ -6063,7 +6063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A2:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6080,7 +6080,6 @@
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -6102,7 +6101,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -7175,7 +7173,6 @@
       </c>
       <c r="L28" s="13" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="24" customHeight="1">
       <c r="B30" s="2" t="inlineStr">
         <is>

--- a/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
+++ b/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
@@ -18,6 +18,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TONG_HOP_VAT_TU_TOAN_BO" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THONG_KE_THEP_CHI_TIET" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAP_PHOI_1M3_VA_TAN_SUAT" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAU_BIEN_BAN_KCS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAU_BB_NGHIEM_THU_VAT_LIEU" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAU_BB_LAY_MAU_HIEN_TRUONG" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +36,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +92,39 @@
       <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="001F497D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -166,7 +202,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -303,11 +339,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F497D"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F497D"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F497D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F497D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -498,6 +548,41 @@
     </xf>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1810,22 +1895,22 @@
           <t>02. KẾT CẤU PHẦN DƯỚI (SUBSTRUCTURE)</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n"/>
-      <c r="C6" s="19" t="n"/>
-      <c r="D6" s="19" t="n"/>
-      <c r="E6" s="19" t="n"/>
-      <c r="F6" s="19" t="n"/>
-      <c r="G6" s="19" t="n"/>
-      <c r="H6" s="19" t="n"/>
-      <c r="I6" s="19" t="n"/>
-      <c r="J6" s="19" t="n"/>
-      <c r="K6" s="19" t="n"/>
-      <c r="L6" s="19" t="n"/>
-      <c r="M6" s="19" t="n"/>
-      <c r="N6" s="19" t="n"/>
-      <c r="O6" s="19" t="n"/>
-      <c r="P6" s="19" t="n"/>
-      <c r="Q6" s="19" t="n"/>
+      <c r="B6" s="49" t="n"/>
+      <c r="C6" s="49" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="49" t="n"/>
+      <c r="K6" s="49" t="n"/>
+      <c r="L6" s="49" t="n"/>
+      <c r="M6" s="49" t="n"/>
+      <c r="N6" s="49" t="n"/>
+      <c r="O6" s="49" t="n"/>
+      <c r="P6" s="49" t="n"/>
+      <c r="Q6" s="50" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -17595,22 +17680,22 @@
           <t>03. KẾT CẤU PHẦN TRÊN (SUPERSTRUCTURE)</t>
         </is>
       </c>
-      <c r="B229" s="19" t="n"/>
-      <c r="C229" s="19" t="n"/>
-      <c r="D229" s="19" t="n"/>
-      <c r="E229" s="19" t="n"/>
-      <c r="F229" s="19" t="n"/>
-      <c r="G229" s="19" t="n"/>
-      <c r="H229" s="19" t="n"/>
-      <c r="I229" s="19" t="n"/>
-      <c r="J229" s="19" t="n"/>
-      <c r="K229" s="19" t="n"/>
-      <c r="L229" s="19" t="n"/>
-      <c r="M229" s="19" t="n"/>
-      <c r="N229" s="19" t="n"/>
-      <c r="O229" s="19" t="n"/>
-      <c r="P229" s="19" t="n"/>
-      <c r="Q229" s="19" t="n"/>
+      <c r="B229" s="49" t="n"/>
+      <c r="C229" s="49" t="n"/>
+      <c r="D229" s="49" t="n"/>
+      <c r="E229" s="49" t="n"/>
+      <c r="F229" s="49" t="n"/>
+      <c r="G229" s="49" t="n"/>
+      <c r="H229" s="49" t="n"/>
+      <c r="I229" s="49" t="n"/>
+      <c r="J229" s="49" t="n"/>
+      <c r="K229" s="49" t="n"/>
+      <c r="L229" s="49" t="n"/>
+      <c r="M229" s="49" t="n"/>
+      <c r="N229" s="49" t="n"/>
+      <c r="O229" s="49" t="n"/>
+      <c r="P229" s="49" t="n"/>
+      <c r="Q229" s="50" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n">
@@ -26493,22 +26578,22 @@
           <t>04. CÔNG TRÌNH PHỤ TRỢ (MISCELLANEOUS)</t>
         </is>
       </c>
-      <c r="B355" s="19" t="n"/>
-      <c r="C355" s="19" t="n"/>
-      <c r="D355" s="19" t="n"/>
-      <c r="E355" s="19" t="n"/>
-      <c r="F355" s="19" t="n"/>
-      <c r="G355" s="19" t="n"/>
-      <c r="H355" s="19" t="n"/>
-      <c r="I355" s="19" t="n"/>
-      <c r="J355" s="19" t="n"/>
-      <c r="K355" s="19" t="n"/>
-      <c r="L355" s="19" t="n"/>
-      <c r="M355" s="19" t="n"/>
-      <c r="N355" s="19" t="n"/>
-      <c r="O355" s="19" t="n"/>
-      <c r="P355" s="19" t="n"/>
-      <c r="Q355" s="19" t="n"/>
+      <c r="B355" s="49" t="n"/>
+      <c r="C355" s="49" t="n"/>
+      <c r="D355" s="49" t="n"/>
+      <c r="E355" s="49" t="n"/>
+      <c r="F355" s="49" t="n"/>
+      <c r="G355" s="49" t="n"/>
+      <c r="H355" s="49" t="n"/>
+      <c r="I355" s="49" t="n"/>
+      <c r="J355" s="49" t="n"/>
+      <c r="K355" s="49" t="n"/>
+      <c r="L355" s="49" t="n"/>
+      <c r="M355" s="49" t="n"/>
+      <c r="N355" s="49" t="n"/>
+      <c r="O355" s="49" t="n"/>
+      <c r="P355" s="49" t="n"/>
+      <c r="Q355" s="50" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="25" t="n">
@@ -29356,22 +29441,22 @@
           <t>01. KẾT CẤU CỌC KHOAN NHỒI (FOUNDATION PILES)</t>
         </is>
       </c>
-      <c r="B396" s="19" t="n"/>
-      <c r="C396" s="19" t="n"/>
-      <c r="D396" s="19" t="n"/>
-      <c r="E396" s="19" t="n"/>
-      <c r="F396" s="19" t="n"/>
-      <c r="G396" s="19" t="n"/>
-      <c r="H396" s="19" t="n"/>
-      <c r="I396" s="19" t="n"/>
-      <c r="J396" s="19" t="n"/>
-      <c r="K396" s="19" t="n"/>
-      <c r="L396" s="19" t="n"/>
-      <c r="M396" s="19" t="n"/>
-      <c r="N396" s="19" t="n"/>
-      <c r="O396" s="19" t="n"/>
-      <c r="P396" s="19" t="n"/>
-      <c r="Q396" s="19" t="n"/>
+      <c r="B396" s="49" t="n"/>
+      <c r="C396" s="49" t="n"/>
+      <c r="D396" s="49" t="n"/>
+      <c r="E396" s="49" t="n"/>
+      <c r="F396" s="49" t="n"/>
+      <c r="G396" s="49" t="n"/>
+      <c r="H396" s="49" t="n"/>
+      <c r="I396" s="49" t="n"/>
+      <c r="J396" s="49" t="n"/>
+      <c r="K396" s="49" t="n"/>
+      <c r="L396" s="49" t="n"/>
+      <c r="M396" s="49" t="n"/>
+      <c r="N396" s="49" t="n"/>
+      <c r="O396" s="49" t="n"/>
+      <c r="P396" s="49" t="n"/>
+      <c r="Q396" s="50" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="25" t="n">
@@ -29592,18 +29677,18 @@
           <t>TỔNG CỘNG CỐT THÉP VÀ CÁP DƯL TOÀN BỘ CÔNG TRÌNH</t>
         </is>
       </c>
-      <c r="B400" s="67" t="n"/>
-      <c r="C400" s="67" t="n"/>
-      <c r="D400" s="67" t="n"/>
-      <c r="E400" s="67" t="n"/>
-      <c r="F400" s="67" t="n"/>
-      <c r="G400" s="67" t="n"/>
-      <c r="H400" s="67" t="n"/>
-      <c r="I400" s="67" t="n"/>
-      <c r="J400" s="67" t="n"/>
-      <c r="K400" s="67" t="n"/>
-      <c r="L400" s="67" t="n"/>
-      <c r="M400" s="67" t="n"/>
+      <c r="B400" s="47" t="n"/>
+      <c r="C400" s="47" t="n"/>
+      <c r="D400" s="47" t="n"/>
+      <c r="E400" s="47" t="n"/>
+      <c r="F400" s="47" t="n"/>
+      <c r="G400" s="47" t="n"/>
+      <c r="H400" s="47" t="n"/>
+      <c r="I400" s="47" t="n"/>
+      <c r="J400" s="47" t="n"/>
+      <c r="K400" s="47" t="n"/>
+      <c r="L400" s="47" t="n"/>
+      <c r="M400" s="48" t="n"/>
       <c r="N400" s="68">
         <f>SUM(N6:N399)</f>
         <v/>
@@ -29958,8 +30043,9 @@
       <c r="I9" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="64" t="n">
-        <v>46.684</v>
+      <c r="J9" s="64">
+        <f>QS_DIEN_GIAI_CHI_TIET!J34</f>
+        <v/>
       </c>
       <c r="K9" s="8">
         <f>J9*E9/1000</f>
@@ -30023,8 +30109,9 @@
       <c r="I10" s="79" t="n">
         <v>2.8</v>
       </c>
-      <c r="J10" s="65" t="n">
-        <v>184.889</v>
+      <c r="J10" s="65">
+        <f>QS_DIEN_GIAI_CHI_TIET!J75*0.026 + 171.659</f>
+        <v/>
       </c>
       <c r="K10" s="26">
         <f>J10*E10/1000</f>
@@ -30088,8 +30175,9 @@
       <c r="I11" s="76" t="n">
         <v>4.1</v>
       </c>
-      <c r="J11" s="64" t="n">
-        <v>1051.33</v>
+      <c r="J11" s="64">
+        <f>QS_DIEN_GIAI_CHI_TIET!J17 + QS_DIEN_GIAI_CHI_TIET!J27</f>
+        <v/>
       </c>
       <c r="K11" s="8">
         <f>J11*E11/1000</f>
@@ -30153,8 +30241,9 @@
       <c r="I12" s="79" t="n">
         <v>3.5</v>
       </c>
-      <c r="J12" s="65" t="n">
-        <v>376.35</v>
+      <c r="J12" s="65">
+        <f>QS_DIEN_GIAI_CHI_TIET!J39*0.395 + QS_DIEN_GIAI_CHI_TIET!J44 + QS_DIEN_GIAI_CHI_TIET!J47</f>
+        <v/>
       </c>
       <c r="K12" s="26">
         <f>J12*E12/1000</f>
@@ -30218,8 +30307,9 @@
       <c r="I13" s="76" t="n">
         <v>3.5</v>
       </c>
-      <c r="J13" s="64" t="n">
-        <v>870.198</v>
+      <c r="J13" s="64">
+        <f>QS_DIEN_GIAI_CHI_TIET!J50 + QS_DIEN_GIAI_CHI_TIET!J39*0.605</f>
+        <v/>
       </c>
       <c r="K13" s="8">
         <f>J13*E13/1000</f>
@@ -30283,8 +30373,9 @@
       <c r="I14" s="79" t="n">
         <v>4.3</v>
       </c>
-      <c r="J14" s="65" t="n">
-        <v>145.026</v>
+      <c r="J14" s="65">
+        <f>QS_DIEN_GIAI_CHI_TIET!J53</f>
+        <v/>
       </c>
       <c r="K14" s="26">
         <f>J14*E14/1000</f>
@@ -30348,8 +30439,9 @@
       <c r="I15" s="76" t="n">
         <v>4.3</v>
       </c>
-      <c r="J15" s="64" t="n">
-        <v>346.713</v>
+      <c r="J15" s="64">
+        <f>QS_DIEN_GIAI_CHI_TIET!J73 + QS_DIEN_GIAI_CHI_TIET!J77 + QS_DIEN_GIAI_CHI_TIET!J79</f>
+        <v/>
       </c>
       <c r="K15" s="8">
         <f>J15*E15/1000</f>
@@ -30413,8 +30505,9 @@
       <c r="I16" s="79" t="n">
         <v>5.7</v>
       </c>
-      <c r="J16" s="65" t="n">
-        <v>434.803</v>
+      <c r="J16" s="65">
+        <f>QS_DIEN_GIAI_CHI_TIET!J62</f>
+        <v/>
       </c>
       <c r="K16" s="26">
         <f>J16*E16/1000</f>
@@ -30513,14 +30606,14 @@
           <t>TỔNG CỘNG TOÀN CÔNG TRÌNH</t>
         </is>
       </c>
-      <c r="B18" s="67" t="n"/>
-      <c r="C18" s="67" t="n"/>
-      <c r="D18" s="67" t="n"/>
-      <c r="E18" s="67" t="n"/>
-      <c r="F18" s="67" t="n"/>
-      <c r="G18" s="67" t="n"/>
-      <c r="H18" s="67" t="n"/>
-      <c r="I18" s="67" t="n"/>
+      <c r="B18" s="47" t="n"/>
+      <c r="C18" s="47" t="n"/>
+      <c r="D18" s="47" t="n"/>
+      <c r="E18" s="47" t="n"/>
+      <c r="F18" s="47" t="n"/>
+      <c r="G18" s="47" t="n"/>
+      <c r="H18" s="47" t="n"/>
+      <c r="I18" s="48" t="n"/>
       <c r="J18" s="69">
         <f>SUM(J9:J17)</f>
         <v/>
@@ -30598,7 +30691,7 @@
       </c>
       <c r="G23" s="71" t="inlineStr">
         <is>
-          <t>Tổng khối lượng toàn cầu</t>
+          <t>Tổng KL công trình</t>
         </is>
       </c>
       <c r="H23" s="71" t="inlineStr">
@@ -30608,7 +30701,7 @@
       </c>
       <c r="I23" s="71" t="inlineStr">
         <is>
-          <t>Số tổ mẫu thí nghiệm bắt buộc</t>
+          <t>Số tổ mẫu thí nghiệm</t>
         </is>
       </c>
       <c r="J23" s="71" t="inlineStr">
@@ -30658,8 +30751,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G24" s="74" t="n">
-        <v>14.53</v>
+      <c r="G24" s="74">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, "&lt;=10")</f>
+        <v/>
       </c>
       <c r="H24" s="74" t="n">
         <v>50</v>
@@ -30715,8 +30809,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G25" s="77" t="n">
-        <v>18.25</v>
+      <c r="G25" s="77">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 12)</f>
+        <v/>
       </c>
       <c r="H25" s="77" t="n">
         <v>50</v>
@@ -30772,8 +30867,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G26" s="74" t="n">
-        <v>14.82</v>
+      <c r="G26" s="74">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 14)</f>
+        <v/>
       </c>
       <c r="H26" s="74" t="n">
         <v>50</v>
@@ -30829,8 +30925,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G27" s="77" t="n">
-        <v>62.48</v>
+      <c r="G27" s="77">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 16)</f>
+        <v/>
       </c>
       <c r="H27" s="77" t="n">
         <v>50</v>
@@ -30886,8 +30983,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G28" s="74" t="n">
-        <v>68.39</v>
+      <c r="G28" s="74">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 18)</f>
+        <v/>
       </c>
       <c r="H28" s="74" t="n">
         <v>50</v>
@@ -30943,8 +31041,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G29" s="77" t="n">
-        <v>15.34</v>
+      <c r="G29" s="77">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 20)</f>
+        <v/>
       </c>
       <c r="H29" s="77" t="n">
         <v>50</v>
@@ -31000,8 +31099,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G30" s="74" t="n">
-        <v>16.92</v>
+      <c r="G30" s="74">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 22)</f>
+        <v/>
       </c>
       <c r="H30" s="74" t="n">
         <v>50</v>
@@ -31057,8 +31157,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G31" s="77" t="n">
-        <v>98.23999999999999</v>
+      <c r="G31" s="77">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 25)</f>
+        <v/>
       </c>
       <c r="H31" s="77" t="n">
         <v>50</v>
@@ -31114,8 +31215,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G32" s="74" t="n">
-        <v>72.09999999999999</v>
+      <c r="G32" s="74">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 28)</f>
+        <v/>
       </c>
       <c r="H32" s="74" t="n">
         <v>50</v>
@@ -31171,8 +31273,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G33" s="77" t="n">
-        <v>53.12</v>
+      <c r="G33" s="77">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 32)</f>
+        <v/>
       </c>
       <c r="H33" s="77" t="n">
         <v>50</v>
@@ -31228,8 +31331,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G34" s="74" t="n">
-        <v>29.91</v>
+      <c r="G34" s="74">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$E$6:$E$399, 15.2)</f>
+        <v/>
       </c>
       <c r="H34" s="74" t="n">
         <v>30</v>
@@ -31285,8 +31389,9 @@
           <t>Tấn</t>
         </is>
       </c>
-      <c r="G35" s="77" t="n">
-        <v>1418.5</v>
+      <c r="G35" s="77">
+        <f>K18</f>
+        <v/>
       </c>
       <c r="H35" s="77" t="n">
         <v>100</v>
@@ -31342,8 +31447,9 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="G36" s="74" t="n">
-        <v>1565.4</v>
+      <c r="G36" s="74">
+        <f>L18</f>
+        <v/>
       </c>
       <c r="H36" s="74" t="n">
         <v>200</v>
@@ -31399,8 +31505,9 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="G37" s="77" t="n">
-        <v>2930.2</v>
+      <c r="G37" s="77">
+        <f>M18</f>
+        <v/>
       </c>
       <c r="H37" s="77" t="n">
         <v>200</v>
@@ -31570,8 +31677,9 @@
           <t>Xe</t>
         </is>
       </c>
-      <c r="G40" s="74" t="n">
-        <v>432</v>
+      <c r="G40" s="74">
+        <f>ROUNDUP(J18/8, 0)</f>
+        <v/>
       </c>
       <c r="H40" s="74" t="n">
         <v>1</v>
@@ -31627,8 +31735,9 @@
           <t>Tổ</t>
         </is>
       </c>
-      <c r="G41" s="77" t="n">
-        <v>1051.3</v>
+      <c r="G41" s="77">
+        <f>J11</f>
+        <v/>
       </c>
       <c r="H41" s="77" t="n">
         <v>20</v>
@@ -31684,8 +31793,9 @@
           <t>Tổ</t>
         </is>
       </c>
-      <c r="G42" s="74" t="n">
-        <v>376.4</v>
+      <c r="G42" s="74">
+        <f>J12</f>
+        <v/>
       </c>
       <c r="H42" s="74" t="n">
         <v>40</v>
@@ -31741,8 +31851,9 @@
           <t>Tổ</t>
         </is>
       </c>
-      <c r="G43" s="77" t="n">
-        <v>870.2</v>
+      <c r="G43" s="77">
+        <f>J13</f>
+        <v/>
       </c>
       <c r="H43" s="77" t="n">
         <v>40</v>
@@ -31798,8 +31909,9 @@
           <t>Tổ</t>
         </is>
       </c>
-      <c r="G44" s="74" t="n">
-        <v>145</v>
+      <c r="G44" s="74">
+        <f>J14</f>
+        <v/>
       </c>
       <c r="H44" s="74" t="n">
         <v>36</v>
@@ -31855,8 +31967,9 @@
           <t>Tổ</t>
         </is>
       </c>
-      <c r="G45" s="77" t="n">
-        <v>434.8</v>
+      <c r="G45" s="77">
+        <f>J16</f>
+        <v/>
       </c>
       <c r="H45" s="77" t="n">
         <v>9.66</v>
@@ -31912,8 +32025,9 @@
           <t>Tổ</t>
         </is>
       </c>
-      <c r="G46" s="74" t="n">
-        <v>346.7</v>
+      <c r="G46" s="74">
+        <f>J15</f>
+        <v/>
       </c>
       <c r="H46" s="74" t="n">
         <v>40</v>
@@ -31969,8 +32083,9 @@
           <t>Tổ</t>
         </is>
       </c>
-      <c r="G47" s="77" t="n">
-        <v>184.9</v>
+      <c r="G47" s="77">
+        <f>J10</f>
+        <v/>
       </c>
       <c r="H47" s="77" t="n">
         <v>40</v>
@@ -32026,8 +32141,9 @@
           <t>Tổ</t>
         </is>
       </c>
-      <c r="G48" s="74" t="n">
-        <v>46.7</v>
+      <c r="G48" s="74">
+        <f>J9</f>
+        <v/>
       </c>
       <c r="H48" s="74" t="n">
         <v>15</v>
@@ -32083,8 +32199,9 @@
           <t>Tổ</t>
         </is>
       </c>
-      <c r="G49" s="77" t="n">
-        <v>4.7</v>
+      <c r="G49" s="77">
+        <f>J17</f>
+        <v/>
       </c>
       <c r="H49" s="77" t="n">
         <v>1.5</v>
@@ -32286,13 +32403,13 @@
           <t>TỔNG SỐ TỔ MẪU THÍ NGHIỆM VÀ PHÉP THỬ KCS BẮT BUỘC TOÀN CÔNG TRÌNH</t>
         </is>
       </c>
-      <c r="B53" s="67" t="n"/>
-      <c r="C53" s="67" t="n"/>
-      <c r="D53" s="67" t="n"/>
-      <c r="E53" s="67" t="n"/>
-      <c r="F53" s="67" t="n"/>
-      <c r="G53" s="67" t="n"/>
-      <c r="H53" s="67" t="n"/>
+      <c r="B53" s="47" t="n"/>
+      <c r="C53" s="47" t="n"/>
+      <c r="D53" s="47" t="n"/>
+      <c r="E53" s="47" t="n"/>
+      <c r="F53" s="47" t="n"/>
+      <c r="G53" s="47" t="n"/>
+      <c r="H53" s="48" t="n"/>
       <c r="I53" s="82">
         <f>SUM(I24:I52)</f>
         <v/>
@@ -32302,14 +32419,739 @@
           <t>Tổng số tổ mẫu nén, kéo uốn và siêu âm KCS hoàn chỉnh</t>
         </is>
       </c>
-      <c r="K53" s="67" t="n"/>
-      <c r="L53" s="67" t="n"/>
+      <c r="K53" s="47" t="n"/>
+      <c r="L53" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="J53:L53"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="84" t="inlineStr">
+        <is>
+          <t>CHỌN SỐ BIÊN BẢN (1 - 22):</t>
+        </is>
+      </c>
+      <c r="C2" s="85" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" s="86" t="inlineStr">
+        <is>
+          <t>(Nhập số thứ tự từ 1 đến 22 để tự động nhảy toàn bộ nội dung biên bản A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="88" t="inlineStr">
+        <is>
+          <t>Độc lập - Tự do - Hạnh phúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>-------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="90" t="inlineStr">
+        <is>
+          <t>BIÊN BẢN NGHIỆM THU CÔNG VIỆC XÂY DỰNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="91">
+        <f>"Số: " &amp; TEXT(C2, "00") &amp; "/BBNT-XD/KM19+529.080"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="86" t="inlineStr">
+        <is>
+          <t>Căn cứ Luật Xây dựng số 135/2025/QH15;</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="86" t="inlineStr">
+        <is>
+          <t>Căn cứ Nghị định số 207/2026/NĐ-CP ngày 15/01/2026 của Chính phủ về quản lý chất lượng công trình;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="86" t="inlineStr">
+        <is>
+          <t>Căn cứ Hợp đồng thi công xây dựng số 09/2026/HĐ-XL gói thầu xây lắp Cầu Km19+529.080;</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="86" t="inlineStr">
+        <is>
+          <t>Căn cứ Hồ sơ thiết kế bản vẽ thi công và Chỉ dẫn kỹ thuật được phê duyệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="84" t="inlineStr">
+        <is>
+          <t>1. Tên công trình / Dự án:</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dự án đầu tư xây dựng đường cao tốc Tuyên Quang - Hà Giang (Giai đoạn 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="84" t="inlineStr">
+        <is>
+          <t>2. Hạng mục công trình:</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CẦU KM19+529.080 (Sơ đồ nhịp 3x39.1m Super-T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="84" t="inlineStr">
+        <is>
+          <t>3. Địa điểm xây dựng:</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Km19+529.080, Tỉnh Hà Giang</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="84" t="inlineStr">
+        <is>
+          <t>4. Đối tượng nghiệm thu:</t>
+        </is>
+      </c>
+      <c r="C19" s="63">
+        <f>VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 3, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="84" t="inlineStr">
+        <is>
+          <t>5. Khối lượng nghiệm thu:</t>
+        </is>
+      </c>
+      <c r="C20" s="84">
+        <f>TEXT(VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 4, FALSE), "#,##0.00") &amp; " " &amp; VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 5, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="84" t="inlineStr">
+        <is>
+          <t>6. Tiêu chuẩn kỹ thuật áp dụng:</t>
+        </is>
+      </c>
+      <c r="C21" s="92">
+        <f>VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 6, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="84" t="inlineStr">
+        <is>
+          <t>7. Thời gian nghiệm thu:</t>
+        </is>
+      </c>
+      <c r="C22" s="92">
+        <f>"Bắt đầu: 08 giờ 30 phút - Kết thúc: 11 giờ 30 phút, ngày " &amp; TEXT(VLOOKUP(C2, HOSO_KCS_NGHIEM_THU!$A$6:$H$27, 8, FALSE), "dd/mm/yyyy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="84" t="inlineStr">
+        <is>
+          <t>8. Thành phần trực tiếp nghiệm thu:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="84" t="inlineStr">
+        <is>
+          <t>a) Đại diện Tư vấn giám sát (TVGS):</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>- Ông: Nguyễn Văn Thắng     - Chức vụ: Kỹ sư Giám sát trưởng</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="84" t="inlineStr">
+        <is>
+          <t>b) Đại diện Nhà thầu thi công:</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>- Ông: Trần Đình Hoàng      - Chức vụ: Chỉ huy trưởng công trường</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>- Ông: Lê Văn Dũng          - Chức vụ: Kỹ sư QA/QC hiện trường</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="84" t="inlineStr">
+        <is>
+          <t>9. Đánh giá kết quả công việc đã thực hiện:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="92" t="inlineStr">
+        <is>
+          <t>- Về kích thước hình học, cao độ, tim mốc: Đạt yêu cầu theo hồ sơ thiết kế bản vẽ thi công.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="92" t="inlineStr">
+        <is>
+          <t>- Về chất lượng vật liệu, chứng chỉ xuất xưởng, kết quả thí nghiệm KCS: Đạt yêu cầu theo tiêu chuẩn áp dụng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="92" t="inlineStr">
+        <is>
+          <t>- Về an toàn lao động, vệ sinh môi trường: Tuân thủ đầy đủ biện pháp thi công được duyệt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="84" t="inlineStr">
+        <is>
+          <t>10. Kết luận nghiệm thu:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="93" t="inlineStr">
+        <is>
+          <t>CHẤP THUẬN NGHIỆM THU CÔNG VIỆC XÂY DỰNG. ĐỒNG Ý CHO PHÉP TRIỂN KHAI BƯỚC THI CÔNG TIẾP THEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="94" t="inlineStr">
+        <is>
+          <t>ĐẠI DIỆN NHÀ THẦU THI CÔNG</t>
+        </is>
+      </c>
+      <c r="E38" s="94" t="inlineStr">
+        <is>
+          <t>ĐẠI DIỆN TƯ VẤN GIÁM SÁT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="95" t="inlineStr">
+        <is>
+          <t>(Ký, ghi rõ họ tên &amp; đóng dấu)</t>
+        </is>
+      </c>
+      <c r="E39" s="95" t="inlineStr">
+        <is>
+          <t>(Ký, ghi rõ họ tên)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="94" t="inlineStr">
+        <is>
+          <t>Trần Đình Hoàng</t>
+        </is>
+      </c>
+      <c r="E44" s="94" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thắng</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="E38:G38"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="84" t="inlineStr">
+        <is>
+          <t>CHỌN MÃ VẬT LIỆU (1 - 16):</t>
+        </is>
+      </c>
+      <c r="C2" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="86" t="inlineStr">
+        <is>
+          <t>(Nhập mã từ 1 đến 16 theo danh mục ma trận tần suất thí nghiệm để tự nhảy biên bản)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="88" t="inlineStr">
+        <is>
+          <t>Độc lập - Tự do - Hạnh phúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="90" t="inlineStr">
+        <is>
+          <t>BIÊN BẢN NGHIỆM THU VẬT LIỆU XÂY DỰNG ĐẦU VÀO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="95">
+        <f>"Số: " &amp; TEXT(C2, "00") &amp; "/BBNT-VL/KM19+529.080"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="84" t="inlineStr">
+        <is>
+          <t>1. Tên vật liệu nghiệm thu:</t>
+        </is>
+      </c>
+      <c r="C12" s="63">
+        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 2, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="84" t="inlineStr">
+        <is>
+          <t>2. Khối lượng nghiệm thu lô hàng:</t>
+        </is>
+      </c>
+      <c r="C13" s="84">
+        <f>TEXT(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 7, FALSE), "#,##0.00") &amp; " " &amp; VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 6, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="84" t="inlineStr">
+        <is>
+          <t>3. Tiêu chuẩn kỹ thuật áp dụng:</t>
+        </is>
+      </c>
+      <c r="C14" s="92">
+        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 3, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="84" t="inlineStr">
+        <is>
+          <t>4. Chỉ tiêu kiểm tra chất lượng:</t>
+        </is>
+      </c>
+      <c r="C15" s="92">
+        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 4, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="84" t="inlineStr">
+        <is>
+          <t>5. Quy cách và số lượng tổ mẫu thí nghiệm:</t>
+        </is>
+      </c>
+      <c r="C16" s="92">
+        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 10, FALSE) &amp; " (Số tổ mẫu: " &amp; VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 9, FALSE) &amp; " tổ)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="84" t="inlineStr">
+        <is>
+          <t>6. Đơn vị thực hiện thí nghiệm:</t>
+        </is>
+      </c>
+      <c r="C17" s="92">
+        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 11, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="84" t="inlineStr">
+        <is>
+          <t>7. Điều kiện nghiệm thu / Chuyển bước:</t>
+        </is>
+      </c>
+      <c r="C18" s="84">
+        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$38, 12, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="84" t="inlineStr">
+        <is>
+          <t>8. Kết luận nghiệm thu:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="93" t="inlineStr">
+        <is>
+          <t>VẬT LIỆU ĐẠT TIÊU CHUẨN KỸ THUẬT THEO QUY ĐỊNH. ĐỒNG Ý CHO PHÉP ĐƯA VÀO SỬ DỤNG TRONG THI CÔNG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="94" t="inlineStr">
+        <is>
+          <t>ĐẠI DIỆN NHÀ THẦU THI CÔNG</t>
+        </is>
+      </c>
+      <c r="E24" s="94" t="inlineStr">
+        <is>
+          <t>ĐẠI DIỆN TƯ VẤN GIÁM SÁT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="94" t="inlineStr">
+        <is>
+          <t>Trần Đình Hoàng</t>
+        </is>
+      </c>
+      <c r="E30" s="94" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thắng</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="C17:G17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="84" t="inlineStr">
+        <is>
+          <t>CHỌN MÃ HẠNG MỤC LẤY MẪU (17 - 26):</t>
+        </is>
+      </c>
+      <c r="C2" s="85" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" s="86" t="inlineStr">
+        <is>
+          <t>(Nhập mã từ 17 đến 26 tương ứng các hạng mục mẫu nén bê tông để tự động điền form)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="84" t="inlineStr">
+        <is>
+          <t>CHỌN NGÀY ĐÚC MẪU (YYYY-MM-DD):</t>
+        </is>
+      </c>
+      <c r="C3" s="97" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="D3" s="86" t="inlineStr">
+        <is>
+          <t>(Tự động tính ngày nén mẫu R7 = Ngày đúc + 7, R28 = Ngày đúc + 28 theo đúng quy định)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="88" t="inlineStr">
+        <is>
+          <t>Độc lập - Tự do - Hạnh phúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="90" t="inlineStr">
+        <is>
+          <t>BIÊN BẢN LẤY MẪU THÍ NGHIỆM TẠI HIỆN TRƯỜNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="95">
+        <f>"Số: " &amp; TEXT(C2, "00") &amp; "/BBLM-HT/KM19+529.080"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="84" t="inlineStr">
+        <is>
+          <t>1. Đối tượng và cấu kiện lấy mẫu:</t>
+        </is>
+      </c>
+      <c r="C12" s="63">
+        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 2, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="84" t="inlineStr">
+        <is>
+          <t>2. Thể tích bê tông / Quy mô mẻ đổ:</t>
+        </is>
+      </c>
+      <c r="C13" s="84">
+        <f>TEXT(VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 7, FALSE), "#,##0.00") &amp; " " &amp; VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 6, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="84" t="inlineStr">
+        <is>
+          <t>3. Quy định số tổ mẫu bắt buộc:</t>
+        </is>
+      </c>
+      <c r="C14" s="84">
+        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 9, FALSE) &amp; " tổ mẫu (" &amp; VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 10, FALSE) &amp; ")"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="84" t="inlineStr">
+        <is>
+          <t>4. Tiêu chuẩn lấy mẫu &amp; thử nghiệm:</t>
+        </is>
+      </c>
+      <c r="C15" s="92">
+        <f>VLOOKUP(C2, CAP_PHOI_1M3_VA_TAN_SUAT!$A$23:$L$51, 3, FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="84" t="inlineStr">
+        <is>
+          <t>5. Phương pháp bảo dưỡng mẫu:</t>
+        </is>
+      </c>
+      <c r="C16" s="92" t="inlineStr">
+        <is>
+          <t>Bảo dưỡng ẩm tiêu chuẩn trong phòng thí nghiệm (TCVN 3105:2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="84" t="inlineStr">
+        <is>
+          <t>6. Kế hoạch nén kiểm tra cường độ:</t>
+        </is>
+      </c>
+      <c r="C17" s="84">
+        <f>"Nén kiểm tra R7 ngày (" &amp; TEXT(DATEVALUE(C3)+7, "dd/mm/yyyy") &amp; "): Đạt &gt;= 70-80% f'c | Nén R28 ngày (" &amp; TEXT(DATEVALUE(C3)+28, "dd/mm/yyyy") &amp; "): Đạt &gt;= 100% f'c"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="84" t="inlineStr">
+        <is>
+          <t>7. Tình trạng mẫu khi bàn giao:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="86" t="inlineStr">
+        <is>
+          <t>Mẫu đúc nguyên vẹn, bề mặt phẳng đều, dán nhãn ghi rõ ngày đúc, vị trí cấu kiện và ký hiệu tổ mẫu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="94" t="inlineStr">
+        <is>
+          <t>CÁN BỘ LẤY MẪU THÍ NGHIỆM (LAS-XD)</t>
+        </is>
+      </c>
+      <c r="E23" s="94" t="inlineStr">
+        <is>
+          <t>KỸ SƯ GIÁM SÁT CHỨNG KIẾN (TVGS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="94" t="inlineStr">
+        <is>
+          <t>Hoàng Trung Kiên</t>
+        </is>
+      </c>
+      <c r="E29" s="94" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thắng</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33656,8 +34498,8 @@
       <c r="G22" s="19" t="n"/>
       <c r="H22" s="19" t="n"/>
       <c r="I22" s="19" t="n"/>
-      <c r="J22" s="20">
-        <f>SUM(J23:J26)</f>
+      <c r="J22" s="83">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Cọc khoan nhồi*")</f>
         <v/>
       </c>
       <c r="K22" s="21" t="n">
@@ -34848,8 +35690,8 @@
       <c r="G56" s="19" t="n"/>
       <c r="H56" s="19" t="n"/>
       <c r="I56" s="19" t="n"/>
-      <c r="J56" s="20">
-        <f>SUM(J57:J60)</f>
+      <c r="J56" s="83">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Mố*") + SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Trụ*")</f>
         <v/>
       </c>
       <c r="K56" s="21" t="n">
@@ -35106,8 +35948,8 @@
       <c r="G64" s="19" t="n"/>
       <c r="H64" s="19" t="n"/>
       <c r="I64" s="19" t="n"/>
-      <c r="J64" s="20">
-        <f>SUM(J65:J65)</f>
+      <c r="J64" s="83">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$D$6:$D$399, "*CABLE*")</f>
         <v/>
       </c>
       <c r="K64" s="21" t="n">
@@ -35179,8 +36021,8 @@
       <c r="G66" s="19" t="n"/>
       <c r="H66" s="19" t="n"/>
       <c r="I66" s="19" t="n"/>
-      <c r="J66" s="20">
-        <f>SUM(J67:J67)</f>
+      <c r="J66" s="83">
+        <f>SUMIFS(THONG_KE_THEP_CHI_TIET!$O$6:$O$399, THONG_KE_THEP_CHI_TIET!$B$6:$B$399, "*Dầm chủ Super-T*", THONG_KE_THEP_CHI_TIET!$D$6:$D$399, "&lt;&gt;*CABLE*")</f>
         <v/>
       </c>
       <c r="K66" s="21" t="n">
@@ -40891,7 +41733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G27"/>
+  <dimension ref="A2:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -40960,6 +41802,11 @@
           <t>Chỉ tiêu thí nghiệm &amp; Điểm kiểm soát (Hold Points)</t>
         </is>
       </c>
+      <c r="H5" s="88" t="inlineStr">
+        <is>
+          <t>Ngày nghiệm thu hoàn thành</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -40995,6 +41842,10 @@
           <t>Sai số tọa độ tim mốc &lt;= 5mm, mốc cao độ &lt;= 2mm</t>
         </is>
       </c>
+      <c r="H6" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J8</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
@@ -41031,6 +41882,10 @@
           <t>Độ dầm chặt nền đường K &gt;= 0.95, thoát nước tốt</t>
         </is>
       </c>
+      <c r="H7" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J10</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="31" t="inlineStr">
@@ -41066,6 +41921,10 @@
           <t>Chứng chỉ CO/CQ, thí nghiệm kéo uốn thép, nén xi măng</t>
         </is>
       </c>
+      <c r="H8" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!I8</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="31" t="inlineStr">
@@ -41101,6 +41960,10 @@
           <t>Độ chính xác cân đong sai số &lt;= 1%, bệ đúc đủ độ cứng</t>
         </is>
       </c>
+      <c r="H9" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J11</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="31" t="inlineStr">
@@ -41119,7 +41982,7 @@
         </is>
       </c>
       <c r="D10" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J13</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J12</f>
         <v/>
       </c>
       <c r="E10" s="31" t="inlineStr">
@@ -41136,6 +41999,10 @@
         <is>
           <t>Độ nghiêng ống vách &lt;= 1%, sai số tim cọc &lt;= 50mm</t>
         </is>
+      </c>
+      <c r="H10" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!I14</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -41172,6 +42039,10 @@
           <t>Khoan vào đá liền khối tối thiểu 5m, không rỗng Karst</t>
         </is>
       </c>
+      <c r="H11" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J13</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="31" t="inlineStr">
@@ -41208,6 +42079,10 @@
           <t>Chiều dày cặn lắng đáy &lt;= 50mm, tỷ trọng bentonite 1.05-1.15</t>
         </is>
       </c>
+      <c r="H12" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J14</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="31" t="inlineStr">
@@ -41226,7 +42101,7 @@
         </is>
       </c>
       <c r="D13" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J23</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J22</f>
         <v/>
       </c>
       <c r="E13" s="31" t="inlineStr">
@@ -41243,6 +42118,10 @@
         <is>
           <t>Chiều dài lồng thép, mối nối coupler, ống siêu âm kín nước</t>
         </is>
+      </c>
+      <c r="H13" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J15</f>
+        <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -41262,7 +42141,7 @@
         </is>
       </c>
       <c r="D14" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J18</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J17</f>
         <v/>
       </c>
       <c r="E14" s="31" t="inlineStr">
@@ -41279,6 +42158,10 @@
         <is>
           <t>Độ sụt 18+-2cm, ống tremie ngập bê tông &gt;= 2.0m liên tục</t>
         </is>
+      </c>
+      <c r="H14" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J17</f>
+        <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -41315,6 +42198,10 @@
           <t>Siêu âm 156 mặt cắt; PDA trụ T1 đạt tải trọng 9434 kN</t>
         </is>
       </c>
+      <c r="H15" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J18</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="31" t="inlineStr">
@@ -41333,7 +42220,7 @@
         </is>
       </c>
       <c r="D16" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J28</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J34</f>
         <v/>
       </c>
       <c r="E16" s="31" t="inlineStr">
@@ -41350,6 +42237,10 @@
         <is>
           <t>Đầu cọc ngàm vào bệ 10cm, cốt thép cọc neo sâu 40D</t>
         </is>
+      </c>
+      <c r="H16" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J20</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -41369,7 +42260,7 @@
         </is>
       </c>
       <c r="D17" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J37</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J39</f>
         <v/>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -41386,6 +42277,10 @@
         <is>
           <t>Kích thước hình học bệ, 12 tổ mẫu thử nén đạt C30</t>
         </is>
+      </c>
+      <c r="H17" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J22</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -41405,7 +42300,7 @@
         </is>
       </c>
       <c r="D18" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J42</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J44</f>
         <v/>
       </c>
       <c r="E18" s="31" t="inlineStr">
@@ -41422,6 +42317,10 @@
         <is>
           <t>Độ thẳng đứng thân mố, bề mặt bê tông phẳng nhẵn</t>
         </is>
+      </c>
+      <c r="H18" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J24</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -41441,7 +42340,7 @@
         </is>
       </c>
       <c r="D19" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J47</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J50</f>
         <v/>
       </c>
       <c r="E19" s="31" t="inlineStr">
@@ -41458,6 +42357,10 @@
         <is>
           <t>Kích thước thân đặc 9.75x2.0m, chiều cao H=14.5m và 11.4m</t>
         </is>
+      </c>
+      <c r="H19" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J23</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -41477,7 +42380,7 @@
         </is>
       </c>
       <c r="D20" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J51</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J53</f>
         <v/>
       </c>
       <c r="E20" s="31" t="inlineStr">
@@ -41494,6 +42397,10 @@
         <is>
           <t>Cao độ mặt đá kê gối sai số &lt;= 2mm, tim đá kê &lt;= 3mm</t>
         </is>
+      </c>
+      <c r="H20" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J25</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -41513,7 +42420,7 @@
         </is>
       </c>
       <c r="D21" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J57</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J62</f>
         <v/>
       </c>
       <c r="E21" s="31" t="inlineStr">
@@ -41530,6 +42437,10 @@
         <is>
           <t>Cường độ bê tông đạt R28 &gt;= 45 MPa, không rỗ nứt</t>
         </is>
+      </c>
+      <c r="H21" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J28</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -41549,7 +42460,7 @@
         </is>
       </c>
       <c r="D22" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J59</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J64</f>
         <v/>
       </c>
       <c r="E22" s="31" t="inlineStr">
@@ -41566,6 +42477,10 @@
         <is>
           <t>Sai số độ giãn dài cáp &lt;= +-5%, vữa bơm lấp đầy 100% gen</t>
         </is>
+      </c>
+      <c r="H22" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J29</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -41585,7 +42500,7 @@
         </is>
       </c>
       <c r="D23" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J65</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J70</f>
         <v/>
       </c>
       <c r="E23" s="31" t="inlineStr">
@@ -41602,6 +42517,10 @@
         <is>
           <t>Gối chậu nằm ngang chuẩn xác, dầm đặt êm thuận trên mố trụ</t>
         </is>
+      </c>
+      <c r="H23" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J31</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -41621,7 +42540,7 @@
         </is>
       </c>
       <c r="D24" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J68</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J73+QS_DIEN_GIAI_CHI_TIET!J79</f>
         <v/>
       </c>
       <c r="E24" s="31" t="inlineStr">
@@ -41638,6 +42557,10 @@
         <is>
           <t>Liên kết cứng dầm ngang, bản liên tục nhiệt triệt tiêu khe nứt</t>
         </is>
+      </c>
+      <c r="H24" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J33</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -41657,7 +42580,7 @@
         </is>
       </c>
       <c r="D25" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J74</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J77</f>
         <v/>
       </c>
       <c r="E25" s="31" t="inlineStr">
@@ -41674,6 +42597,10 @@
         <is>
           <t>Độ dốc ngang thoát nước 2%, chiều dày bảo vệ cốt thép chuẩn</t>
         </is>
+      </c>
+      <c r="H25" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J35</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -41693,7 +42620,7 @@
         </is>
       </c>
       <c r="D26" s="42">
-        <f>QS_DIEN_GIAI_CHI_TIET!J87</f>
+        <f>QS_DIEN_GIAI_CHI_TIET!J84+QS_DIEN_GIAI_CHI_TIET!J86</f>
         <v/>
       </c>
       <c r="E26" s="31" t="inlineStr">
@@ -41710,6 +42637,10 @@
         <is>
           <t>Độ bằng phẳng mặt cầu IRI &lt;= 1.5, khe răng lược êm thuận</t>
         </is>
+      </c>
+      <c r="H26" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J39</f>
+        <v/>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -41745,6 +42676,10 @@
         <is>
           <t>Độ võng tĩnh f &lt;= f_cp, hệ số xung kích động đạt tiêu chuẩn</t>
         </is>
+      </c>
+      <c r="H27" s="96">
+        <f>TIEN_DO_THI_CONG_WBS!J42</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
+++ b/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
@@ -1063,8 +1063,9 @@
       <c r="C6" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>480</v>
+      <c r="D6" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,25,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*Cọc khoan nhồi*")</f>
+        <v/>
       </c>
       <c r="E6" s="8" t="n">
         <v>11.2</v>
@@ -1111,8 +1112,9 @@
       <c r="C7" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>620</v>
+      <c r="D7" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*đai tăng cường cọc*")</f>
+        <v/>
       </c>
       <c r="E7" s="8" t="n">
         <v>3.85</v>
@@ -1159,8 +1161,9 @@
       <c r="C8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>850</v>
+      <c r="D8" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,10,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*đai xoắn*")</f>
+        <v/>
       </c>
       <c r="E8" s="8" t="n">
         <v>2.9</v>
@@ -1207,8 +1210,9 @@
       <c r="C9" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>240</v>
+      <c r="D9" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,32,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*đáy bệ móng*")</f>
+        <v/>
       </c>
       <c r="E9" s="8" t="n">
         <v>5.75</v>
@@ -1255,8 +1259,9 @@
       <c r="C10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>310</v>
+      <c r="D10" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,20,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*phân bố bệ*")</f>
+        <v/>
       </c>
       <c r="E10" s="8" t="n">
         <v>8.4</v>
@@ -1303,8 +1308,9 @@
       <c r="C11" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>180</v>
+      <c r="D11" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,28,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*thân mố*")</f>
+        <v/>
       </c>
       <c r="E11" s="8" t="n">
         <v>7.8</v>
@@ -1351,8 +1357,9 @@
       <c r="C12" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>320</v>
+      <c r="D12" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,32,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*thân đặc trụ*")</f>
+        <v/>
       </c>
       <c r="E12" s="8" t="n">
         <v>9.6</v>
@@ -1399,8 +1406,9 @@
       <c r="C13" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>160</v>
+      <c r="D13" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,28,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*xà mũ trụ*")</f>
+        <v/>
       </c>
       <c r="E13" s="8" t="n">
         <v>10.5</v>
@@ -1447,8 +1455,9 @@
       <c r="C14" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>960</v>
+      <c r="D14" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*thường dầm Super-T*")</f>
+        <v/>
       </c>
       <c r="E14" s="8" t="n">
         <v>7.85</v>
@@ -1495,8 +1504,9 @@
       <c r="C15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1200</v>
+      <c r="D15" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,14,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*thường dầm Super-T*")</f>
+        <v/>
       </c>
       <c r="E15" s="8" t="n">
         <v>3.8</v>
@@ -1543,8 +1553,9 @@
       <c r="C16" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>450</v>
+      <c r="D16" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*dầm ngang*")</f>
+        <v/>
       </c>
       <c r="E16" s="8" t="n">
         <v>5.6</v>
@@ -1591,8 +1602,9 @@
       <c r="C17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D17" s="7" t="n">
-        <v>1450</v>
+      <c r="D17" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*bản mặt cầu*")</f>
+        <v/>
       </c>
       <c r="E17" s="8" t="n">
         <v>3.85</v>
@@ -1639,8 +1651,9 @@
       <c r="C18" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>1550</v>
+      <c r="D18" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,14,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*bản mặt cầu*")</f>
+        <v/>
       </c>
       <c r="E18" s="8" t="n">
         <v>3.85</v>
@@ -1687,8 +1700,9 @@
       <c r="C19" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D19" s="7" t="n">
-        <v>260</v>
+      <c r="D19" s="7">
+        <f>COUNTIFS(THONG_KE_THEP_CHI_TIET!$E$6:$E$399,16,THONG_KE_THEP_CHI_TIET!$B$6:$B$399,"*bản quá độ*")</f>
+        <v/>
       </c>
       <c r="E19" s="8" t="n">
         <v>7.85</v>
@@ -30571,8 +30585,9 @@
       <c r="I17" s="76" t="n">
         <v>4.5</v>
       </c>
-      <c r="J17" s="64" t="n">
-        <v>4.674</v>
+      <c r="J17" s="64">
+        <f>QS_DIEN_GIAI_CHI_TIET!J86</f>
+        <v/>
       </c>
       <c r="K17" s="8">
         <f>J17*E17/1000</f>
@@ -31563,8 +31578,9 @@
           <t>Nguồn</t>
         </is>
       </c>
-      <c r="G38" s="74" t="n">
-        <v>1</v>
+      <c r="G38" s="74">
+        <f>N18</f>
+        <v/>
       </c>
       <c r="H38" s="74" t="n">
         <v>1</v>
@@ -31620,8 +31636,9 @@
           <t>Lô</t>
         </is>
       </c>
-      <c r="G39" s="77" t="n">
-        <v>3</v>
+      <c r="G39" s="77">
+        <f>O18</f>
+        <v/>
       </c>
       <c r="H39" s="77" t="n">
         <v>1</v>

--- a/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
+++ b/templates/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
@@ -357,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -584,6 +584,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -34863,7 +34864,7 @@
       <c r="B33" s="23" t="n"/>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>- Khối lượng đào đất đá móng bệ mố trụ (Link ô F19 Sheet KHOI_LUONG_DAO_DAP)</t>
+          <t>- Đào đất đá hố móng bệ mố M1,M2 &amp; bệ trụ T1,T2 → =KHOI_LUONG_DAO_DAP!F21</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr">
@@ -34886,8 +34887,8 @@
       <c r="I33" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="28">
-        <f>E33*F33*G33*H33*I33</f>
+      <c r="J33" s="98">
+        <f>KHOI_LUONG_DAO_DAP!F21</f>
         <v/>
       </c>
       <c r="K33" s="23" t="n"/>
@@ -37324,7 +37325,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ Thông tư 11/2021/TT-BXD, Thông tư 12/2021/TT-BXD, Luật Xây dựng số 135/2025/QH15 &amp; NĐ 207/2026/NĐ-CP</t>
+          <t>Căn cứ Thông tư 11/2021/TT-BXD, Luật Xây dựng 135/2025/QH15, Nghị định 207/2026/NĐ-CP</t>
         </is>
       </c>
     </row>
@@ -37578,7 +37579,7 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>VAT = G x 8,00%</t>
+          <t>VAT = G x 10,00% (Luật Xây dựng 135/2025)</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
@@ -37587,12 +37588,12 @@
         </is>
       </c>
       <c r="E13" s="21">
-        <f>E12*0.08</f>
+        <f>E12*0.10</f>
         <v/>
       </c>
       <c r="F13" s="31" t="inlineStr">
         <is>
-          <t>Chính sách thuế hiện hành</t>
+          <t>Áp dụng từ 01/01/2026 - Luật số 135/2025/QH15</t>
         </is>
       </c>
     </row>
